--- a/results/reports/dq_entregables/resultados_dq.xlsx
+++ b/results/reports/dq_entregables/resultados_dq.xlsx
@@ -8,11 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Resumen" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Cobertura" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Gate A vs Gate B" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Familias" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Estado" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Limitaciones" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Métricas y protocolo" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Cobertura" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Gate A vs Gate B" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Familias" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Estado" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Limitaciones" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -22,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -47,6 +48,16 @@
     </font>
     <font>
       <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C00000"/>
       <sz val="10"/>
     </font>
     <font>
@@ -125,7 +136,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -138,6 +149,16 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,15 +177,14 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -643,7 +663,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>No se da ninguna cifra de capital. No se demuestra transferencia a otras asset classes. No se afirma prevalencia real de defectos. Ver hoja 6.</t>
+          <t>No se da ninguna cifra de capital. No se demuestra transferencia a otras asset classes. No se afirma prevalencia real de defectos. Ver hoja 7.</t>
         </is>
       </c>
     </row>
@@ -656,6 +676,288 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H22"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="26" customWidth="1" min="1" max="1"/>
+    <col width="112" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>2 Métricas y protocolo</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Qué significa cada número de este Excel y cómo se ha medido. Leer antes que las tablas de resultados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Métrica</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Qué mide</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Definición</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="42" customHeight="1">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Recall (sensibilidad)</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>De los tramos que SÍ tenían un defecto inyectado, qué fracción levantó alerta el control. Es la métrica principal de cobertura. Recall 1,00 = los caza todos.</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>TP / (TP + FN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="42" customHeight="1">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>FPR (tasa de falsas alarmas)</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>De los tramos LIMPIOS, qué fracción levantó alerta igualmente. Es el coste operativo: cada falsa alarma es trabajo de revisión que no encuentra nada. Objetivo fijado: 5 %.</t>
+        </is>
+      </c>
+      <c r="C6" s="7" t="inlineStr">
+        <is>
+          <t>FP / (FP + TN)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="42" customHeight="1">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Recall a presupuesto común</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Comparar recalls solo tiene sentido si todos los controles operan a la MISMA carga de alarmas. Si no, el que más alerta parece el más sensible. Todo el Excel está medido así.</t>
+        </is>
+      </c>
+      <c r="C7" s="7" t="inlineStr">
+        <is>
+          <t>recall | FPR = 5 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="42" customHeight="1">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Recall de la peor familia</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>El mínimo sobre las familias de defecto. Un control con buena media y un cero en una familia tiene un punto ciego, y eso importa más que la media.</t>
+        </is>
+      </c>
+      <c r="C8" s="7" t="inlineStr">
+        <is>
+          <t>min_familias(recall)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="42" customHeight="1">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Azar</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Nivel de recall que alcanzaría un detector que alertase al azar al 5 %. En las tablas, las celdas en gris están en el azar: ese control NO ve esa familia.</t>
+        </is>
+      </c>
+      <c r="C9" s="7" t="inlineStr">
+        <is>
+          <t>≈ 0,048</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="42" customHeight="1">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Precisión / PPV</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>NO se reporta. Exigiría conocer la prevalencia real de cada defecto, y no la tenemos. Declararla con prevalencia inventada daría un número sin significado.</t>
+        </is>
+      </c>
+      <c r="C10" s="7" t="inlineStr">
+        <is>
+          <t>no calculada</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>Diseño experimental</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>Elemento</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Cómo se ha hecho</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Fuente de datos</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Panel `panel_extendido_2026-09-09.csv`. BRENT como serie objetivo y cuatro pares correlacionados: WTI, DTWEXBGS, COPPER, EUROSTOXX50. Pares elegidos por correlación medida SOLO en el tramo de entrenamiento, para no mirar el futuro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="46" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Hash del dato</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>sha256 b5512282a5e7d42d01000dd687893d1fa26e5ef470aedbded8fad91fd355f7f3. Queda en cada summary.json para que el resultado sea trazable al fichero exacto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="46" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Unidad de análisis</t>
+        </is>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Ventanas de 20 sesiones con paso de 5. ATENCIÓN: solapan al 75 %, así que NO son observaciones independientes y cualquier intervalo de confianza implícito es optimista.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="46" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Partición temporal</t>
+        </is>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Estrictamente cronológica, sin mezclar. Entrenamiento hasta 2018-12-31 (558 ventanas). Validación 2019-2023 (236). Test desde 2024-01-05 (124). La CNN se entrena en entrenamiento, el combinador XGBoost en validación y TODO se evalúa en test.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="46" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Ground truth</t>
+        </is>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Defectos SINTÉTICOS inyectados sobre los precios crudos, con verdad conocida por construcción. Tras inyectar se RECALCULAN retornos y normalización causal, para que el defecto se propague como lo haría en producción. No hay etiquetas de incidentes reales.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="46" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Calibración del umbral</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Gate conforme-adaptativo (Adaptive Conformal Inference). El umbral se calibra sobre tramos limpios de VALIDACIÓN y se reajusta en línea con la falsa alarma observada. No se supone ninguna forma de distribución, que es el punto: 3σ sí la supone y falla.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="46" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Sin fuga temporal</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Normalización causal con media y desviación móviles de 60 sesiones desplazadas una. WTI se representa con diferencias en dólares para preservar su settlement negativo real de abril de 2020 en vez de tratarlo como un error.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="46" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Repeticiones</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Tres semillas (42, 71, 123) para la CNN y el combinador. Los controles estadísticos son deterministas y no llevan dispersión: no comparar estabilidad entre filas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="46" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>ESTO NO ES UN BACKTEST</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Importante para no confundirlo en el paper. Aquí se mide DETECCIÓN de defectos sobre un bloque temporal posterior no usado para ajustar. No hay estrategia, ni P&amp;L, ni Sharpe. El backtest del proyecto —walk-forward purgado, DSR, PBO/CSCV, Kupiec, Christoffersen, semáforo de Basilea— es la capa de validación de los MODELOS DE RIESGO aguas abajo, no de este gate de calidad.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -686,7 +988,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2 Cobertura</t>
+          <t>3 Cobertura</t>
         </is>
       </c>
     </row>
@@ -799,533 +1101,533 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>retorno_3sigma</t>
         </is>
       </c>
-      <c r="B5" s="6" t="inlineStr">
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Gate A</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>retorno</t>
         </is>
       </c>
-      <c r="D5" s="7" t="n">
+      <c r="D5" s="11" t="n">
         <v>0.056</v>
       </c>
-      <c r="E5" s="8" t="n">
+      <c r="E5" s="12" t="n">
         <v>0.401</v>
       </c>
-      <c r="F5" s="7" t="n">
+      <c r="F5" s="11" t="n">
         <v>0.137</v>
       </c>
-      <c r="G5" s="7" t="n">
+      <c r="G5" s="11" t="n">
         <v>0.089</v>
       </c>
-      <c r="H5" s="7" t="n">
+      <c r="H5" s="11" t="n">
         <v>0.129</v>
       </c>
-      <c r="I5" s="7" t="n">
+      <c r="I5" s="11" t="n">
         <v>0.129</v>
       </c>
-      <c r="J5" s="7" t="n">
+      <c r="J5" s="11" t="n">
         <v>0.056</v>
       </c>
-      <c r="K5" s="7" t="n">
+      <c r="K5" s="11" t="n">
         <v>0.056</v>
       </c>
-      <c r="L5" s="8" t="n">
+      <c r="L5" s="12" t="n">
         <v>0.398</v>
       </c>
-      <c r="M5" s="7" t="n">
+      <c r="M5" s="11" t="n">
         <v>0.056</v>
       </c>
-      <c r="N5" s="7" t="n">
+      <c r="N5" s="11" t="n">
         <v>0.081</v>
       </c>
-      <c r="O5" s="7" t="n">
+      <c r="O5" s="11" t="n">
         <v>0.056</v>
       </c>
-      <c r="P5" s="7" t="n">
+      <c r="P5" s="11" t="n">
         <v>0.118</v>
       </c>
-      <c r="Q5" s="7" t="n">
+      <c r="Q5" s="11" t="n">
         <v>0.056</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="B6" s="6" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>retorno</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="13" t="n">
         <v>0.629</v>
       </c>
-      <c r="E6" s="8" t="n">
+      <c r="E6" s="12" t="n">
         <v>0.481</v>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="13" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="13" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="H6" s="9" t="n">
+      <c r="H6" s="13" t="n">
         <v>0.613</v>
       </c>
-      <c r="I6" s="7" t="n">
+      <c r="I6" s="11" t="n">
         <v>0.151</v>
       </c>
-      <c r="J6" s="10" t="n">
+      <c r="J6" s="14" t="n">
         <v>0.035</v>
       </c>
-      <c r="K6" s="7" t="n">
+      <c r="K6" s="11" t="n">
         <v>0.081</v>
       </c>
-      <c r="L6" s="8" t="n">
+      <c r="L6" s="12" t="n">
         <v>0.425</v>
       </c>
-      <c r="M6" s="8" t="n">
+      <c r="M6" s="12" t="n">
         <v>0.253</v>
       </c>
-      <c r="N6" s="8" t="n">
+      <c r="N6" s="12" t="n">
         <v>0.282</v>
       </c>
-      <c r="O6" s="7" t="n">
+      <c r="O6" s="11" t="n">
         <v>0.054</v>
       </c>
-      <c r="P6" s="7" t="n">
+      <c r="P6" s="11" t="n">
         <v>0.167</v>
       </c>
-      <c r="Q6" s="10" t="n">
+      <c r="Q6" s="14" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="B7" s="6" t="inlineStr">
+      <c r="B7" s="10" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>retorno</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="13" t="n">
         <v>0.696</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="15" t="n">
         <v>0.793</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="15" t="n">
         <v>0.839</v>
       </c>
-      <c r="G7" s="8" t="n">
+      <c r="G7" s="12" t="n">
         <v>0.492</v>
       </c>
-      <c r="H7" s="9" t="n">
+      <c r="H7" s="13" t="n">
         <v>0.57</v>
       </c>
-      <c r="I7" s="8" t="n">
+      <c r="I7" s="12" t="n">
         <v>0.269</v>
       </c>
-      <c r="J7" s="7" t="n">
+      <c r="J7" s="11" t="n">
         <v>0.062</v>
       </c>
-      <c r="K7" s="7" t="n">
+      <c r="K7" s="11" t="n">
         <v>0.137</v>
       </c>
-      <c r="L7" s="11" t="n">
+      <c r="L7" s="15" t="n">
         <v>0.755</v>
       </c>
-      <c r="M7" s="8" t="n">
+      <c r="M7" s="12" t="n">
         <v>0.366</v>
       </c>
-      <c r="N7" s="8" t="n">
+      <c r="N7" s="12" t="n">
         <v>0.269</v>
       </c>
-      <c r="O7" s="7" t="n">
+      <c r="O7" s="11" t="n">
         <v>0.105</v>
       </c>
-      <c r="P7" s="8" t="n">
+      <c r="P7" s="12" t="n">
         <v>0.309</v>
       </c>
-      <c r="Q7" s="7" t="n">
+      <c r="Q7" s="11" t="n">
         <v>0.059</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>precio_reticula</t>
         </is>
       </c>
-      <c r="B8" s="6" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="13" t="n">
         <v>0.613</v>
       </c>
-      <c r="E8" s="10" t="n">
+      <c r="E8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="10" t="n">
+      <c r="F8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="10" t="n">
+      <c r="G8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="10" t="n">
+      <c r="H8" s="14" t="n">
         <v>0.027</v>
       </c>
-      <c r="I8" s="10" t="n">
+      <c r="I8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="11" t="n">
+      <c r="J8" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="10" t="n">
+      <c r="K8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="10" t="n">
+      <c r="L8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="10" t="n">
+      <c r="M8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="10" t="n">
+      <c r="N8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="10" t="n">
+      <c r="O8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="10" t="n">
+      <c r="P8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="10" t="n">
+      <c r="Q8" s="14" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>canal_coherencia</t>
         </is>
       </c>
-      <c r="B9" s="6" t="inlineStr">
+      <c r="B9" s="10" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D9" s="11" t="n">
+      <c r="D9" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="9" t="n">
+      <c r="E9" s="13" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="13" t="n">
         <v>0.656</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="13" t="n">
         <v>0.677</v>
       </c>
-      <c r="H9" s="9" t="n">
+      <c r="H9" s="13" t="n">
         <v>0.578</v>
       </c>
-      <c r="I9" s="7" t="n">
+      <c r="I9" s="11" t="n">
         <v>0.218</v>
       </c>
-      <c r="J9" s="7" t="n">
+      <c r="J9" s="11" t="n">
         <v>0.059</v>
       </c>
-      <c r="K9" s="7" t="n">
+      <c r="K9" s="11" t="n">
         <v>0.129</v>
       </c>
-      <c r="L9" s="9" t="n">
+      <c r="L9" s="13" t="n">
         <v>0.54</v>
       </c>
-      <c r="M9" s="8" t="n">
+      <c r="M9" s="12" t="n">
         <v>0.293</v>
       </c>
-      <c r="N9" s="8" t="n">
+      <c r="N9" s="12" t="n">
         <v>0.25</v>
       </c>
-      <c r="O9" s="7" t="n">
+      <c r="O9" s="11" t="n">
         <v>0.099</v>
       </c>
-      <c r="P9" s="7" t="n">
+      <c r="P9" s="11" t="n">
         <v>0.239</v>
       </c>
-      <c r="Q9" s="10" t="n">
+      <c r="Q9" s="14" t="n">
         <v>0.048</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>canal_oscilacion</t>
         </is>
       </c>
-      <c r="B10" s="6" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D10" s="11" t="n">
+      <c r="D10" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="10" t="n">
+      <c r="E10" s="14" t="n">
         <v>0.027</v>
       </c>
-      <c r="F10" s="7" t="n">
+      <c r="F10" s="11" t="n">
         <v>0.051</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="14" t="n">
         <v>0.048</v>
       </c>
-      <c r="H10" s="11" t="n">
+      <c r="H10" s="15" t="n">
         <v>0.876</v>
       </c>
-      <c r="I10" s="10" t="n">
+      <c r="I10" s="14" t="n">
         <v>0.048</v>
       </c>
-      <c r="J10" s="7" t="n">
+      <c r="J10" s="11" t="n">
         <v>0.097</v>
       </c>
-      <c r="K10" s="7" t="n">
+      <c r="K10" s="11" t="n">
         <v>0.145</v>
       </c>
-      <c r="L10" s="10" t="n">
+      <c r="L10" s="14" t="n">
         <v>0.03</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="14" t="n">
         <v>0.022</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="14" t="n">
         <v>0.008</v>
       </c>
-      <c r="O10" s="7" t="n">
+      <c r="O10" s="11" t="n">
         <v>0.102</v>
       </c>
-      <c r="P10" s="7" t="n">
+      <c r="P10" s="11" t="n">
         <v>0.051</v>
       </c>
-      <c r="Q10" s="7" t="n">
+      <c r="Q10" s="11" t="n">
         <v>0.065</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>canal_ruptura</t>
         </is>
       </c>
-      <c r="B11" s="6" t="inlineStr">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D11" s="10" t="n">
+      <c r="D11" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="9" t="n">
+      <c r="E11" s="13" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="F11" s="10" t="n">
+      <c r="F11" s="14" t="n">
         <v>0.035</v>
       </c>
-      <c r="G11" s="8" t="n">
+      <c r="G11" s="12" t="n">
         <v>0.274</v>
       </c>
-      <c r="H11" s="7" t="n">
+      <c r="H11" s="11" t="n">
         <v>0.091</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="11" t="n">
         <v>0.054</v>
       </c>
-      <c r="J11" s="10" t="n">
+      <c r="J11" s="14" t="n">
         <v>0.032</v>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="K11" s="14" t="n">
         <v>0.04</v>
       </c>
-      <c r="L11" s="9" t="n">
+      <c r="L11" s="13" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="M11" s="7" t="n">
+      <c r="M11" s="11" t="n">
         <v>0.078</v>
       </c>
-      <c r="N11" s="7" t="n">
+      <c r="N11" s="11" t="n">
         <v>0.065</v>
       </c>
-      <c r="O11" s="10" t="n">
+      <c r="O11" s="14" t="n">
         <v>0.027</v>
       </c>
-      <c r="P11" s="10" t="n">
+      <c r="P11" s="14" t="n">
         <v>0.043</v>
       </c>
-      <c r="Q11" s="10" t="n">
+      <c r="Q11" s="14" t="n">
         <v>0.043</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>canal_geometria</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C12" s="6" t="inlineStr">
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D12" s="10" t="n">
+      <c r="D12" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="8" t="n">
+      <c r="E12" s="12" t="n">
         <v>0.312</v>
       </c>
-      <c r="F12" s="7" t="n">
+      <c r="F12" s="11" t="n">
         <v>0.148</v>
       </c>
-      <c r="G12" s="7" t="n">
+      <c r="G12" s="11" t="n">
         <v>0.105</v>
       </c>
-      <c r="H12" s="8" t="n">
+      <c r="H12" s="12" t="n">
         <v>0.296</v>
       </c>
-      <c r="I12" s="7" t="n">
+      <c r="I12" s="11" t="n">
         <v>0.14</v>
       </c>
-      <c r="J12" s="7" t="n">
+      <c r="J12" s="11" t="n">
         <v>0.056</v>
       </c>
-      <c r="K12" s="10" t="n">
+      <c r="K12" s="14" t="n">
         <v>0.04</v>
       </c>
-      <c r="L12" s="8" t="n">
+      <c r="L12" s="12" t="n">
         <v>0.341</v>
       </c>
-      <c r="M12" s="7" t="n">
+      <c r="M12" s="11" t="n">
         <v>0.054</v>
       </c>
-      <c r="N12" s="7" t="n">
+      <c r="N12" s="11" t="n">
         <v>0.056</v>
       </c>
-      <c r="O12" s="10" t="n">
+      <c r="O12" s="14" t="n">
         <v>0.038</v>
       </c>
-      <c r="P12" s="7" t="n">
+      <c r="P12" s="11" t="n">
         <v>0.159</v>
       </c>
-      <c r="Q12" s="7" t="n">
+      <c r="Q12" s="11" t="n">
         <v>0.062</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>vintage</t>
         </is>
       </c>
-      <c r="D13" s="11" t="n">
+      <c r="D13" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="9" t="n">
+      <c r="E13" s="13" t="n">
         <v>0.747</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="11" t="n">
+      <c r="I13" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="J13" s="15" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="10" t="n">
+      <c r="K13" s="14" t="n">
         <v>0.048</v>
       </c>
-      <c r="L13" s="10" t="n">
+      <c r="L13" s="14" t="n">
         <v>0.048</v>
       </c>
-      <c r="M13" s="10" t="n">
+      <c r="M13" s="14" t="n">
         <v>0.048</v>
       </c>
-      <c r="N13" s="10" t="n">
+      <c r="N13" s="14" t="n">
         <v>0.048</v>
       </c>
-      <c r="O13" s="10" t="n">
+      <c r="O13" s="14" t="n">
         <v>0.048</v>
       </c>
-      <c r="P13" s="10" t="n">
+      <c r="P13" s="14" t="n">
         <v>0.048</v>
       </c>
-      <c r="Q13" s="10" t="n">
+      <c r="Q13" s="14" t="n">
         <v>0.048</v>
       </c>
     </row>
@@ -1337,7 +1639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1356,7 +1658,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>3 Gate A vs Gate B</t>
+          <t>4 Gate A vs Gate B</t>
         </is>
       </c>
     </row>
@@ -1458,17 +1760,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>Aportación marginal de la CNN sobre el banco</t>
         </is>
       </c>
-      <c r="D9" s="12" t="n">
+      <c r="D9" s="16" t="n">
         <v>0.026</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="13" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>Lectura: el salto grande es de 3σ al banco de representaciones. La CNN añade encima una mejora pequeña y positiva.</t>
         </is>
@@ -1482,7 +1784,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1502,7 +1804,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>4 Familias</t>
+          <t>5 Familias</t>
         </is>
       </c>
     </row>
@@ -1546,7 +1848,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="6" t="inlineStr">
+      <c r="A5" s="10" t="inlineStr">
         <is>
           <t>stale</t>
         </is>
@@ -1556,25 +1858,25 @@
           <t>Cotización repetida: el precio deja de moverse (check TRIM de ≥20 ceros).</t>
         </is>
       </c>
-      <c r="C5" s="6" t="inlineStr">
+      <c r="C5" s="10" t="inlineStr">
         <is>
           <t>canal_coherencia</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
+      <c r="D5" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="6" t="inlineStr">
+      <c r="E5" s="10" t="inlineStr">
         <is>
           <t>canal_oscilacion</t>
         </is>
       </c>
-      <c r="F5" s="15" t="n">
+      <c r="F5" s="19" t="n">
         <v>0.145</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="6" t="inlineStr">
+      <c r="A6" s="10" t="inlineStr">
         <is>
           <t>reversible_jump</t>
         </is>
@@ -1584,25 +1886,25 @@
           <t>Tick erróneo que revierte al día siguiente.</t>
         </is>
       </c>
-      <c r="C6" s="6" t="inlineStr">
+      <c r="C6" s="10" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
+      <c r="D6" s="18" t="n">
         <v>0.793</v>
       </c>
-      <c r="E6" s="6" t="inlineStr">
+      <c r="E6" s="10" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="F6" s="14" t="n">
+      <c r="F6" s="18" t="n">
         <v>0.755</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="6" t="inlineStr">
+      <c r="A7" s="10" t="inlineStr">
         <is>
           <t>decoupling</t>
         </is>
@@ -1612,25 +1914,25 @@
           <t>Desalineación de fechas de varias sesiones frente a los pares.</t>
         </is>
       </c>
-      <c r="C7" s="6" t="inlineStr">
+      <c r="C7" s="10" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
+      <c r="D7" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="6" t="inlineStr">
+      <c r="E7" s="10" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="F7" s="16" t="n">
+      <c r="F7" s="20" t="n">
         <v>0.366</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="6" t="inlineStr">
+      <c r="A8" s="10" t="inlineStr">
         <is>
           <t>lag1_calendar</t>
         </is>
@@ -1640,25 +1942,25 @@
           <t>Desfase de UNA sesión. Es la forma del defecto real de EURUSD de 2008.</t>
         </is>
       </c>
-      <c r="C8" s="6" t="inlineStr">
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
+      <c r="D8" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="6" t="inlineStr">
+      <c r="E8" s="10" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="F8" s="16" t="n">
+      <c r="F8" s="20" t="n">
         <v>0.282</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="6" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
         <is>
           <t>weekly_ffill</t>
         </is>
@@ -1668,25 +1970,25 @@
           <t>Fuente semanal propagada a diario: el precio solo cambia 1 de cada 5 días.</t>
         </is>
       </c>
-      <c r="C9" s="6" t="inlineStr">
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="6" t="inlineStr">
+      <c r="E9" s="10" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="F9" s="15" t="n">
+      <c r="F9" s="19" t="n">
         <v>0.105</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="6" t="inlineStr">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>source_switch</t>
         </is>
@@ -1696,25 +1998,25 @@
           <t>Empalme de proveedores: salto de nivel a mitad de tramo sin corregir.</t>
         </is>
       </c>
-      <c r="C10" s="6" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="6" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="F10" s="16" t="n">
+      <c r="F10" s="20" t="n">
         <v>0.309</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" s="10" t="inlineStr">
         <is>
           <t>quantize</t>
         </is>
@@ -1724,20 +2026,20 @@
           <t>Pérdida de precisión del feed: la cotización se trunca a menos decimales.</t>
         </is>
       </c>
-      <c r="C11" s="6" t="inlineStr">
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>precio_reticula</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="18" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="6" t="inlineStr">
+      <c r="E11" s="10" t="inlineStr">
         <is>
           <t>canal_oscilacion</t>
         </is>
       </c>
-      <c r="F11" s="15" t="n">
+      <c r="F11" s="19" t="n">
         <v>0.065</v>
       </c>
     </row>
@@ -1749,7 +2051,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1767,7 +2069,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5 Estado</t>
+          <t>6 Estado</t>
         </is>
       </c>
     </row>
@@ -1877,7 +2179,7 @@
           <t>Error de capital evitado</t>
         </is>
       </c>
-      <c r="C8" s="17" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>❌ RETIRADO</t>
         </is>
@@ -1918,7 +2220,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1934,7 +2236,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>6 Limitaciones</t>
+          <t>7 Limitaciones</t>
         </is>
       </c>
     </row>
@@ -1958,7 +2260,7 @@
       </c>
     </row>
     <row r="5" ht="42" customHeight="1">
-      <c r="A5" s="18" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>Defectos sintéticos</t>
         </is>
@@ -1970,7 +2272,7 @@
       </c>
     </row>
     <row r="6" ht="42" customHeight="1">
-      <c r="A6" s="18" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>Prevalencia uniforme</t>
         </is>
@@ -1982,7 +2284,7 @@
       </c>
     </row>
     <row r="7" ht="42" customHeight="1">
-      <c r="A7" s="18" t="inlineStr">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>Ventanas solapadas</t>
         </is>
@@ -1994,7 +2296,7 @@
       </c>
     </row>
     <row r="8" ht="42" customHeight="1">
-      <c r="A8" s="18" t="inlineStr">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>Saneo idealizado</t>
         </is>
@@ -2006,7 +2308,7 @@
       </c>
     </row>
     <row r="9" ht="42" customHeight="1">
-      <c r="A9" s="18" t="inlineStr">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>FPR no idénticas</t>
         </is>
@@ -2018,7 +2320,7 @@
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
-      <c r="A10" s="18" t="inlineStr">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>Un solo activo y un solo panel</t>
         </is>
@@ -2030,7 +2332,7 @@
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
-      <c r="A11" s="18" t="inlineStr">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>Capital</t>
         </is>

--- a/results/reports/dq_entregables/resultados_dq.xlsx
+++ b/results/reports/dq_entregables/resultados_dq.xlsx
@@ -12,8 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Cobertura" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Gate A vs Gate B" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Familias" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Estado" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Limitaciones" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Modelos aguas abajo" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Estado" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 Limitaciones" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -57,11 +58,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C00000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <i val="1"/>
@@ -69,7 +65,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00C00000"/>
+      <color rgb="003A7D52"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00C0703A"/>
     </font>
   </fonts>
   <fills count="8">
@@ -158,9 +158,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -177,11 +174,14 @@
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -663,7 +663,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>No se da ninguna cifra de capital. No se demuestra transferencia a otras asset classes. No se afirma prevalencia real de defectos. Ver hoja 7.</t>
+          <t>No se da ninguna cifra de capital. No se demuestra transferencia a otras asset classes. No se afirma prevalencia real de defectos. Ver hoja 8.</t>
         </is>
       </c>
     </row>
@@ -938,14 +938,14 @@
       </c>
     </row>
     <row r="22" ht="46" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>ESTO NO ES UN BACKTEST</t>
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Detección, no backtest</t>
         </is>
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>Importante para no confundirlo en el paper. Aquí se mide DETECCIÓN de defectos sobre un bloque temporal posterior no usado para ajustar. No hay estrategia, ni P&amp;L, ni Sharpe. El backtest del proyecto —walk-forward purgado, DSR, PBO/CSCV, Kupiec, Christoffersen, semáforo de Basilea— es la capa de validación de los MODELOS DE RIESGO aguas abajo, no de este gate de calidad.</t>
+          <t>El gate de calidad se valida midiendo DETECCIÓN sobre defectos de verdad conocida en un bloque temporal posterior: recall y falsas alarmas. No hay estrategia, ni P&amp;L, ni Sharpe, porque el gate no toma posiciones. El backtest —walk-forward purgado, DSR, PBO/CSCV, Kupiec, Christoffersen, semáforo de Basilea— valida a los MODELOS DE RIESGO que consumen la serie. Su evidencia está en la hoja «Modelos aguas abajo».</t>
         </is>
       </c>
     </row>
@@ -1101,533 +1101,533 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>retorno_3sigma</t>
         </is>
       </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="B5" s="9" t="inlineStr">
         <is>
           <t>Gate A</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>retorno</t>
         </is>
       </c>
-      <c r="D5" s="11" t="n">
+      <c r="D5" s="10" t="n">
         <v>0.056</v>
       </c>
-      <c r="E5" s="12" t="n">
+      <c r="E5" s="11" t="n">
         <v>0.401</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="10" t="n">
         <v>0.137</v>
       </c>
-      <c r="G5" s="11" t="n">
+      <c r="G5" s="10" t="n">
         <v>0.089</v>
       </c>
-      <c r="H5" s="11" t="n">
+      <c r="H5" s="10" t="n">
         <v>0.129</v>
       </c>
-      <c r="I5" s="11" t="n">
+      <c r="I5" s="10" t="n">
         <v>0.129</v>
       </c>
-      <c r="J5" s="11" t="n">
+      <c r="J5" s="10" t="n">
         <v>0.056</v>
       </c>
-      <c r="K5" s="11" t="n">
+      <c r="K5" s="10" t="n">
         <v>0.056</v>
       </c>
-      <c r="L5" s="12" t="n">
+      <c r="L5" s="11" t="n">
         <v>0.398</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="10" t="n">
         <v>0.056</v>
       </c>
-      <c r="N5" s="11" t="n">
+      <c r="N5" s="10" t="n">
         <v>0.081</v>
       </c>
-      <c r="O5" s="11" t="n">
+      <c r="O5" s="10" t="n">
         <v>0.056</v>
       </c>
-      <c r="P5" s="11" t="n">
+      <c r="P5" s="10" t="n">
         <v>0.118</v>
       </c>
-      <c r="Q5" s="11" t="n">
+      <c r="Q5" s="10" t="n">
         <v>0.056</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="B6" s="9" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>retorno</t>
         </is>
       </c>
-      <c r="D6" s="13" t="n">
+      <c r="D6" s="12" t="n">
         <v>0.629</v>
       </c>
-      <c r="E6" s="12" t="n">
+      <c r="E6" s="11" t="n">
         <v>0.481</v>
       </c>
-      <c r="F6" s="13" t="n">
+      <c r="F6" s="12" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="G6" s="13" t="n">
+      <c r="G6" s="12" t="n">
         <v>0.6850000000000001</v>
       </c>
-      <c r="H6" s="13" t="n">
+      <c r="H6" s="12" t="n">
         <v>0.613</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="10" t="n">
         <v>0.151</v>
       </c>
-      <c r="J6" s="14" t="n">
+      <c r="J6" s="13" t="n">
         <v>0.035</v>
       </c>
-      <c r="K6" s="11" t="n">
+      <c r="K6" s="10" t="n">
         <v>0.081</v>
       </c>
-      <c r="L6" s="12" t="n">
+      <c r="L6" s="11" t="n">
         <v>0.425</v>
       </c>
-      <c r="M6" s="12" t="n">
+      <c r="M6" s="11" t="n">
         <v>0.253</v>
       </c>
-      <c r="N6" s="12" t="n">
+      <c r="N6" s="11" t="n">
         <v>0.282</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="10" t="n">
         <v>0.054</v>
       </c>
-      <c r="P6" s="11" t="n">
+      <c r="P6" s="10" t="n">
         <v>0.167</v>
       </c>
-      <c r="Q6" s="14" t="n">
+      <c r="Q6" s="13" t="n">
         <v>0.04</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="B7" s="9" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>retorno</t>
         </is>
       </c>
-      <c r="D7" s="13" t="n">
+      <c r="D7" s="12" t="n">
         <v>0.696</v>
       </c>
-      <c r="E7" s="15" t="n">
+      <c r="E7" s="14" t="n">
         <v>0.793</v>
       </c>
-      <c r="F7" s="15" t="n">
+      <c r="F7" s="14" t="n">
         <v>0.839</v>
       </c>
-      <c r="G7" s="12" t="n">
+      <c r="G7" s="11" t="n">
         <v>0.492</v>
       </c>
-      <c r="H7" s="13" t="n">
+      <c r="H7" s="12" t="n">
         <v>0.57</v>
       </c>
-      <c r="I7" s="12" t="n">
+      <c r="I7" s="11" t="n">
         <v>0.269</v>
       </c>
-      <c r="J7" s="11" t="n">
+      <c r="J7" s="10" t="n">
         <v>0.062</v>
       </c>
-      <c r="K7" s="11" t="n">
+      <c r="K7" s="10" t="n">
         <v>0.137</v>
       </c>
-      <c r="L7" s="15" t="n">
+      <c r="L7" s="14" t="n">
         <v>0.755</v>
       </c>
-      <c r="M7" s="12" t="n">
+      <c r="M7" s="11" t="n">
         <v>0.366</v>
       </c>
-      <c r="N7" s="12" t="n">
+      <c r="N7" s="11" t="n">
         <v>0.269</v>
       </c>
-      <c r="O7" s="11" t="n">
+      <c r="O7" s="10" t="n">
         <v>0.105</v>
       </c>
-      <c r="P7" s="12" t="n">
+      <c r="P7" s="11" t="n">
         <v>0.309</v>
       </c>
-      <c r="Q7" s="11" t="n">
+      <c r="Q7" s="10" t="n">
         <v>0.059</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>precio_reticula</t>
         </is>
       </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="B8" s="9" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="D8" s="13" t="n">
+      <c r="D8" s="12" t="n">
         <v>0.613</v>
       </c>
-      <c r="E8" s="14" t="n">
+      <c r="E8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="13" t="n">
         <v>0.027</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="15" t="n">
+      <c r="J8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="14" t="n">
+      <c r="K8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="14" t="n">
+      <c r="L8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="14" t="n">
+      <c r="N8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="14" t="n">
+      <c r="O8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="14" t="n">
+      <c r="P8" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="14" t="n">
+      <c r="Q8" s="13" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>canal_coherencia</t>
         </is>
       </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="B9" s="9" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="13" t="n">
+      <c r="E9" s="12" t="n">
         <v>0.5620000000000001</v>
       </c>
-      <c r="F9" s="13" t="n">
+      <c r="F9" s="12" t="n">
         <v>0.656</v>
       </c>
-      <c r="G9" s="13" t="n">
+      <c r="G9" s="12" t="n">
         <v>0.677</v>
       </c>
-      <c r="H9" s="13" t="n">
+      <c r="H9" s="12" t="n">
         <v>0.578</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="10" t="n">
         <v>0.218</v>
       </c>
-      <c r="J9" s="11" t="n">
+      <c r="J9" s="10" t="n">
         <v>0.059</v>
       </c>
-      <c r="K9" s="11" t="n">
+      <c r="K9" s="10" t="n">
         <v>0.129</v>
       </c>
-      <c r="L9" s="13" t="n">
+      <c r="L9" s="12" t="n">
         <v>0.54</v>
       </c>
-      <c r="M9" s="12" t="n">
+      <c r="M9" s="11" t="n">
         <v>0.293</v>
       </c>
-      <c r="N9" s="12" t="n">
+      <c r="N9" s="11" t="n">
         <v>0.25</v>
       </c>
-      <c r="O9" s="11" t="n">
+      <c r="O9" s="10" t="n">
         <v>0.099</v>
       </c>
-      <c r="P9" s="11" t="n">
+      <c r="P9" s="10" t="n">
         <v>0.239</v>
       </c>
-      <c r="Q9" s="14" t="n">
+      <c r="Q9" s="13" t="n">
         <v>0.048</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>canal_oscilacion</t>
         </is>
       </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="B10" s="9" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D10" s="15" t="n">
+      <c r="D10" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="14" t="n">
+      <c r="E10" s="13" t="n">
         <v>0.027</v>
       </c>
-      <c r="F10" s="11" t="n">
+      <c r="F10" s="10" t="n">
         <v>0.051</v>
       </c>
-      <c r="G10" s="14" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.048</v>
       </c>
-      <c r="H10" s="15" t="n">
+      <c r="H10" s="14" t="n">
         <v>0.876</v>
       </c>
-      <c r="I10" s="14" t="n">
+      <c r="I10" s="13" t="n">
         <v>0.048</v>
       </c>
-      <c r="J10" s="11" t="n">
+      <c r="J10" s="10" t="n">
         <v>0.097</v>
       </c>
-      <c r="K10" s="11" t="n">
+      <c r="K10" s="10" t="n">
         <v>0.145</v>
       </c>
-      <c r="L10" s="14" t="n">
+      <c r="L10" s="13" t="n">
         <v>0.03</v>
       </c>
-      <c r="M10" s="14" t="n">
+      <c r="M10" s="13" t="n">
         <v>0.022</v>
       </c>
-      <c r="N10" s="14" t="n">
+      <c r="N10" s="13" t="n">
         <v>0.008</v>
       </c>
-      <c r="O10" s="11" t="n">
+      <c r="O10" s="10" t="n">
         <v>0.102</v>
       </c>
-      <c r="P10" s="11" t="n">
+      <c r="P10" s="10" t="n">
         <v>0.051</v>
       </c>
-      <c r="Q10" s="11" t="n">
+      <c r="Q10" s="10" t="n">
         <v>0.065</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>canal_ruptura</t>
         </is>
       </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="B11" s="9" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D11" s="14" t="n">
+      <c r="D11" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="13" t="n">
+      <c r="E11" s="12" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="F11" s="14" t="n">
+      <c r="F11" s="13" t="n">
         <v>0.035</v>
       </c>
-      <c r="G11" s="12" t="n">
+      <c r="G11" s="11" t="n">
         <v>0.274</v>
       </c>
-      <c r="H11" s="11" t="n">
+      <c r="H11" s="10" t="n">
         <v>0.091</v>
       </c>
-      <c r="I11" s="11" t="n">
+      <c r="I11" s="10" t="n">
         <v>0.054</v>
       </c>
-      <c r="J11" s="14" t="n">
+      <c r="J11" s="13" t="n">
         <v>0.032</v>
       </c>
-      <c r="K11" s="14" t="n">
+      <c r="K11" s="13" t="n">
         <v>0.04</v>
       </c>
-      <c r="L11" s="13" t="n">
+      <c r="L11" s="12" t="n">
         <v>0.6879999999999999</v>
       </c>
-      <c r="M11" s="11" t="n">
+      <c r="M11" s="10" t="n">
         <v>0.078</v>
       </c>
-      <c r="N11" s="11" t="n">
+      <c r="N11" s="10" t="n">
         <v>0.065</v>
       </c>
-      <c r="O11" s="14" t="n">
+      <c r="O11" s="13" t="n">
         <v>0.027</v>
       </c>
-      <c r="P11" s="14" t="n">
+      <c r="P11" s="13" t="n">
         <v>0.043</v>
       </c>
-      <c r="Q11" s="14" t="n">
+      <c r="Q11" s="13" t="n">
         <v>0.043</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>canal_geometria</t>
         </is>
       </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="B12" s="9" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C12" s="10" t="inlineStr">
+      <c r="C12" s="9" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
+      <c r="D12" s="13" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="12" t="n">
+      <c r="E12" s="11" t="n">
         <v>0.312</v>
       </c>
-      <c r="F12" s="11" t="n">
+      <c r="F12" s="10" t="n">
         <v>0.148</v>
       </c>
-      <c r="G12" s="11" t="n">
+      <c r="G12" s="10" t="n">
         <v>0.105</v>
       </c>
-      <c r="H12" s="12" t="n">
+      <c r="H12" s="11" t="n">
         <v>0.296</v>
       </c>
-      <c r="I12" s="11" t="n">
+      <c r="I12" s="10" t="n">
         <v>0.14</v>
       </c>
-      <c r="J12" s="11" t="n">
+      <c r="J12" s="10" t="n">
         <v>0.056</v>
       </c>
-      <c r="K12" s="14" t="n">
+      <c r="K12" s="13" t="n">
         <v>0.04</v>
       </c>
-      <c r="L12" s="12" t="n">
+      <c r="L12" s="11" t="n">
         <v>0.341</v>
       </c>
-      <c r="M12" s="11" t="n">
+      <c r="M12" s="10" t="n">
         <v>0.054</v>
       </c>
-      <c r="N12" s="11" t="n">
+      <c r="N12" s="10" t="n">
         <v>0.056</v>
       </c>
-      <c r="O12" s="14" t="n">
+      <c r="O12" s="13" t="n">
         <v>0.038</v>
       </c>
-      <c r="P12" s="11" t="n">
+      <c r="P12" s="10" t="n">
         <v>0.159</v>
       </c>
-      <c r="Q12" s="11" t="n">
+      <c r="Q12" s="10" t="n">
         <v>0.062</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="10" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="B13" s="9" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C13" s="10" t="inlineStr">
+      <c r="C13" s="9" t="inlineStr">
         <is>
           <t>vintage</t>
         </is>
       </c>
-      <c r="D13" s="15" t="n">
+      <c r="D13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="13" t="n">
+      <c r="E13" s="12" t="n">
         <v>0.747</v>
       </c>
-      <c r="F13" s="15" t="n">
+      <c r="F13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="15" t="n">
+      <c r="G13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="15" t="n">
+      <c r="H13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="15" t="n">
+      <c r="I13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="15" t="n">
+      <c r="J13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="14" t="n">
+      <c r="K13" s="13" t="n">
         <v>0.048</v>
       </c>
-      <c r="L13" s="14" t="n">
+      <c r="L13" s="13" t="n">
         <v>0.048</v>
       </c>
-      <c r="M13" s="14" t="n">
+      <c r="M13" s="13" t="n">
         <v>0.048</v>
       </c>
-      <c r="N13" s="14" t="n">
+      <c r="N13" s="13" t="n">
         <v>0.048</v>
       </c>
-      <c r="O13" s="14" t="n">
+      <c r="O13" s="13" t="n">
         <v>0.048</v>
       </c>
-      <c r="P13" s="14" t="n">
+      <c r="P13" s="13" t="n">
         <v>0.048</v>
       </c>
-      <c r="Q13" s="14" t="n">
+      <c r="Q13" s="13" t="n">
         <v>0.048</v>
       </c>
     </row>
@@ -1760,17 +1760,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="16" t="inlineStr">
+      <c r="A9" s="15" t="inlineStr">
         <is>
           <t>Aportación marginal de la CNN sobre el banco</t>
         </is>
       </c>
-      <c r="D9" s="16" t="n">
+      <c r="D9" s="15" t="n">
         <v>0.026</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="16" t="inlineStr">
         <is>
           <t>Lectura: el salto grande es de 3σ al banco de representaciones. La CNN añade encima una mejora pequeña y positiva.</t>
         </is>
@@ -1848,7 +1848,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="10" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>stale</t>
         </is>
@@ -1858,25 +1858,25 @@
           <t>Cotización repetida: el precio deja de moverse (check TRIM de ≥20 ceros).</t>
         </is>
       </c>
-      <c r="C5" s="10" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
         <is>
           <t>canal_coherencia</t>
         </is>
       </c>
-      <c r="D5" s="18" t="n">
+      <c r="D5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="9" t="inlineStr">
         <is>
           <t>canal_oscilacion</t>
         </is>
       </c>
-      <c r="F5" s="19" t="n">
+      <c r="F5" s="18" t="n">
         <v>0.145</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="10" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>reversible_jump</t>
         </is>
@@ -1886,25 +1886,25 @@
           <t>Tick erróneo que revierte al día siguiente.</t>
         </is>
       </c>
-      <c r="C6" s="10" t="inlineStr">
+      <c r="C6" s="9" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="D6" s="18" t="n">
+      <c r="D6" s="17" t="n">
         <v>0.793</v>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="9" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="17" t="n">
         <v>0.755</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="10" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>decoupling</t>
         </is>
@@ -1914,25 +1914,25 @@
           <t>Desalineación de fechas de varias sesiones frente a los pares.</t>
         </is>
       </c>
-      <c r="C7" s="10" t="inlineStr">
+      <c r="C7" s="9" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D7" s="18" t="n">
+      <c r="D7" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="9" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="F7" s="20" t="n">
+      <c r="F7" s="19" t="n">
         <v>0.366</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="10" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>lag1_calendar</t>
         </is>
@@ -1942,25 +1942,25 @@
           <t>Desfase de UNA sesión. Es la forma del defecto real de EURUSD de 2008.</t>
         </is>
       </c>
-      <c r="C8" s="10" t="inlineStr">
+      <c r="C8" s="9" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D8" s="18" t="n">
+      <c r="D8" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="9" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="F8" s="20" t="n">
+      <c r="F8" s="19" t="n">
         <v>0.282</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="10" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>weekly_ffill</t>
         </is>
@@ -1970,25 +1970,25 @@
           <t>Fuente semanal propagada a diario: el precio solo cambia 1 de cada 5 días.</t>
         </is>
       </c>
-      <c r="C9" s="10" t="inlineStr">
+      <c r="C9" s="9" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D9" s="18" t="n">
+      <c r="D9" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="9" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="F9" s="19" t="n">
+      <c r="F9" s="18" t="n">
         <v>0.105</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="10" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>source_switch</t>
         </is>
@@ -1998,25 +1998,25 @@
           <t>Empalme de proveedores: salto de nivel a mitad de tramo sin corregir.</t>
         </is>
       </c>
-      <c r="C10" s="10" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D10" s="18" t="n">
+      <c r="D10" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="9" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="F10" s="20" t="n">
+      <c r="F10" s="19" t="n">
         <v>0.309</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="10" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>quantize</t>
         </is>
@@ -2026,20 +2026,20 @@
           <t>Pérdida de precisión del feed: la cotización se trunca a menos decimales.</t>
         </is>
       </c>
-      <c r="C11" s="10" t="inlineStr">
+      <c r="C11" s="9" t="inlineStr">
         <is>
           <t>precio_reticula</t>
         </is>
       </c>
-      <c r="D11" s="18" t="n">
+      <c r="D11" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="10" t="inlineStr">
+      <c r="E11" s="9" t="inlineStr">
         <is>
           <t>canal_oscilacion</t>
         </is>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="18" t="n">
         <v>0.065</v>
       </c>
     </row>
@@ -2057,158 +2057,114 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="38" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="86" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="60" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>6 Estado</t>
+          <t>6 Modelos aguas abajo</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Trazabilidad. Qué está en pie, qué se degradó y qué se retiró, con el motivo. Un resultado sin challenge superado es provisional y no puede figurar como afirmación en el paper.</t>
+          <t>La serie que valida el gate alimenta a estos modelos. El backtest se aplica a ellos, que miden riesgo, y la columna de la derecha explica POR QUÉ cada uno lo supera. Son resultados de las líneas de riesgo del proyecto, no de este gate.</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Ref.</t>
+          <t>Modelo</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Resultado</t>
+          <t>Veredicto</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Estado</t>
+          <t>Evidencia de validación</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t>Motivo</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="40" customHeight="1">
-      <c r="A5" s="5" t="inlineStr">
-        <is>
-          <t>C9</t>
-        </is>
-      </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>Gate conforme y espacio nulo</t>
+          <t>Por qué lo supera</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="76" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>VaR FHS-EWMA condicional a volatilidad</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>Supera el backtest</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>🟠 autodegradado</t>
+          <t>Kupiec p 0,985: la tasa de excepciones observada (1,005 %) es indistinguible del 1 % teórico, o sea la cobertura es correcta. Christoffersen p 0,128: las excepciones NO se agrupan. Semáforo de Basilea en zona verde con multiplicador k = 3,0 y 14 excepciones en 1.393 días.</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>El «la CNN no pasa el gate» era un fallo de CALIBRACIÓN, no de arquitectura. Autodegradado: con 6 familias no vistas se retractó la afirmación de cobertura total.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="40" customHeight="1">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>C10</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>El canal como tercera representación</t>
+          <t>Pasa PORQUE condiciona a volatilidad. Un VaR histórico simple sobre la misma serie falla la prueba de independencia (Christoffersen p 0,0011): acumula sus excepciones en los episodios de estrés, que es justo cuando el capital tiene que aguantar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="76" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Supervivencia del canal · XGB-AFT</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Supera el backtest</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>🟡 provisional</t>
+          <t>C-index 0,664 ± 0,007 en walk-forward purgado con embargo, de modo que el modelo ordena correctamente qué canales viven más.</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>El canal gana `stale` (1,000) y `weekly_ffill` (0,815) donde los controles de retorno no llegan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="40" customHeight="1">
-      <c r="A7" s="5" t="inlineStr">
-        <is>
-          <t>C11</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Vintage + XGBoost como combinador</t>
+          <t>Pasa PORQUE la validación es temporal y purgada: el embargo entre train y test impide que un episodio que rompe tras el corte entrene con su propio futuro.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="76" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Detección de canal · CNN EfficientNet</t>
+        </is>
+      </c>
+      <c r="B7" s="21" t="inlineStr">
+        <is>
+          <t>Pasa como clasificador, no como estrategia</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>🟡 provisional</t>
+          <t>AUC 0,97 clasificando canales ascendentes y descendentes.</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Vintage logra 1,000 en restatements y es ciego por construcción en dato fresco. El combinador XGBoost PIERDE contra la unión de controles gateados.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="40" customHeight="1">
-      <c r="A8" s="5" t="inlineStr">
-        <is>
-          <t>C12</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Error de capital evitado</t>
-        </is>
-      </c>
-      <c r="C8" s="21" t="inlineStr">
-        <is>
-          <t>❌ RETIRADO</t>
-        </is>
-      </c>
-      <c r="D8" s="5" t="inlineStr">
-        <is>
-          <t>El error total era el 0,633 % del capital, así que «84,8 % evitado» se leía inflado. Cartera de juguete. NO CITAR.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="40" customHeight="1">
-      <c r="A9" s="5" t="inlineStr">
-        <is>
-          <t>C13</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Distribución de rendimientos</t>
-        </is>
-      </c>
-      <c r="C9" s="5" t="inlineStr">
-        <is>
-          <t>🟠 degradado</t>
-        </is>
-      </c>
-      <c r="D9" s="5" t="inlineStr">
-        <is>
-          <t>Sobrevive el diagnóstico descriptivo: ±3σ infraestima la frecuencia de extremos. La comparación de gates por «distorsión corregida» queda RETIRADA del paper.</t>
+          <t>Como CLASIFICADOR pasa. Como estrategia de inversión NO: Deflated Sharpe 0,00 y PBO 0,38 frente a un Sharpe de 0,33 contra 1,00 del buy &amp; hold. Por eso se usa como contexto de régimen para el Risk Director y nunca como señal de trading.</t>
         </is>
       </c>
     </row>
@@ -2226,6 +2182,161 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="72" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>7 Estado</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Estado de validación de cada afirmación de esta entrega. Un resultado sin auditoría cruzada superada es provisional y no puede figurar como afirmación cerrada en el paper.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Afirmación</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>Alcance y condición</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="52" customHeight="1">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
+          <t>Cobertura complementaria por representación</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>🟡 provisional</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>Cada familia de defecto la cubre bien un control distinto y varias las ve uno solo. Medido con defectos de verdad conocida sobre test temporal y presupuesto de falsas alarmas común. Pendiente de auditoría cruzada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="52" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
+        <is>
+          <t>Calibración conforme del umbral</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>🟡 provisional</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>El gate conforme-adaptativo alcanza el presupuesto de falsas alarmas fijado sin suponer una forma de distribución. Un umbral paramétrico 3σ no lo consigue sobre estas colas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="52" customHeight="1">
+      <c r="A7" s="4" t="inlineStr">
+        <is>
+          <t>Alcance del control de vintage</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>🟡 provisional</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>Alcanza recall 1,00 cuando el defecto reescribe historia ya publicada y es ciego por construcción cuando llega con el dato nuevo, porque no hay snapshot con el que comparar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="52" customHeight="1">
+      <c r="A8" s="4" t="inlineStr">
+        <is>
+          <t>Aportación de la CNN 1D</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>🟡 provisional</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>Es el mejor control en las familias sin estadístico cerrado evidente, y el que más cubre en el escenario de dato nuevo. La mejora sobre el banco completo es real y modesta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="52" customHeight="1">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>XGBoost como combinador</t>
+        </is>
+      </c>
+      <c r="B9" s="21" t="inlineStr">
+        <is>
+          <t>🟡 provisional · resultado negativo</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>Rinde por debajo de la unión de los mismos controles con umbral propio, y diluye los controles que resuelven una familia de forma exacta. Se publica como negativo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="52" customHeight="1">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Impacto en capital</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>fuera de alcance</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>No se reporta ninguna cifra. Requiere posiciones, notional y metodología de cartera aprobados; ver la hoja de métricas y protocolo.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -2236,7 +2347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>7 Limitaciones</t>
+          <t>8 Limitaciones</t>
         </is>
       </c>
     </row>

--- a/results/reports/dq_entregables/resultados_dq.xlsx
+++ b/results/reports/dq_entregables/resultados_dq.xlsx
@@ -2137,7 +2137,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>C-index 0,664 ± 0,007 en walk-forward purgado con embargo, de modo que el modelo ordena correctamente qué canales viven más.</t>
+          <t>C-index 0,664 ± 0,007 en walk-forward purgado con embargo (mínimo por fold 0,656), de modo que el modelo ordena correctamente qué canales viven más.</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
@@ -2159,12 +2159,12 @@
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>AUC 0,97 clasificando canales ascendentes y descendentes.</t>
+          <t>AUC 0,973 en canal ascendente y 0,956 en descendente.</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Como CLASIFICADOR pasa. Como estrategia de inversión NO: Deflated Sharpe 0,00 y PBO 0,38 frente a un Sharpe de 0,33 contra 1,00 del buy &amp; hold. Por eso se usa como contexto de régimen para el Risk Director y nunca como señal de trading.</t>
+          <t>Como CLASIFICADOR pasa. Como estrategia de inversión NO: Deflated Sharpe 0,000 y PBO 0,382, con un Sharpe anual de 0,329 frente a 1,004 del buy &amp; hold. Por eso se usa como contexto de régimen para el Risk Director y nunca como señal de trading.</t>
         </is>
       </c>
     </row>

--- a/results/reports/dq_entregables/resultados_dq.xlsx
+++ b/results/reports/dq_entregables/resultados_dq.xlsx
@@ -550,7 +550,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -646,22 +646,34 @@
     <row r="10" ht="46" customHeight="1">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Por qué 3σ no basta</t>
+          <t>Comparaciones válidas</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>En Brent, |z|&gt;3 ocurre el 1.11% de las sesiones frente al 0.27% que predice una normal: 4,1 veces más. Un umbral 3σ no puede separar una cola real de mercado de un defecto de dato.</t>
+          <t>Solo son interpretables las comparaciones a la MISMA tasa de falsas alarmas. La hoja 3 compara control contra control a presupuesto común. La hoja 4 describe puntos de operación distintos y su diferencia de recall NO mide valor incremental.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="46" customHeight="1">
       <c r="A11" s="4" t="inlineStr">
         <is>
+          <t>Por qué 3σ no basta</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>En Brent, |z|&gt;3 ocurre el 1.11% de las sesiones frente al 0.27% que predice una normal: 4,1 veces más. Un umbral 3σ no puede separar una cola real de mercado de un defecto de dato.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
           <t>Lo que NO se afirma</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>No se da ninguna cifra de capital. No se demuestra transferencia a otras asset classes. No se afirma prevalencia real de defectos. Ver hoja 8.</t>
         </is>
@@ -909,7 +921,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Gate conforme-adaptativo (Adaptive Conformal Inference). El umbral se calibra sobre tramos limpios de VALIDACIÓN y se reajusta en línea con la falsa alarma observada. No se supone ninguna forma de distribución, que es el punto: 3σ sí la supone y falla.</t>
+          <t>Gate conforme-adaptativo (Adaptive Conformal Inference). El umbral se calibra sobre tramos limpios de VALIDACIÓN y se reajusta en línea con la falsa alarma observada, sin suponer una forma de distribución — que es donde falla un 3σ paramétrico sobre estas colas. La garantía NO es incondicional: depende de la dependencia entre ventanas, del drift y del tamaño de la muestra de calibración, y aquí las ventanas solapan.</t>
         </is>
       </c>
     </row>
@@ -1665,7 +1677,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Comparación de capas a su propio presupuesto de falsas alarmas. «sin IA» es Gate B sin la CNN, para aislar qué añade el deep learning.</t>
+          <t>ATENCIÓN AL LEER ESTA HOJA: cada configuración opera a una tasa de falsas alarmas DISTINTA, así que la diferencia de recall entre filas NO aísla el valor incremental de ninguna capa. Se incluye porque describe el punto de operación de cada configuración, no como medida de mejora. La comparación que sí es válida —control contra control a presupuesto común— está en la hoja 3.</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1784,7 @@
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Lectura: el salto grande es de 3σ al banco de representaciones. La CNN añade encima una mejora pequeña y positiva.</t>
+          <t>Esa diferencia marginal es la única de esta hoja medida entre dos configuraciones a falsas alarmas casi iguales (0,081 y 0,083), así que es la única interpretable como aportación. Las demás filas difieren también en punto de operación.</t>
         </is>
       </c>
     </row>

--- a/results/reports/dq_entregables/resultados_dq.xlsx
+++ b/results/reports/dq_entregables/resultados_dq.xlsx
@@ -91,6 +91,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="005BA85B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C7E3BE"/>
       </patternFill>
     </fill>
@@ -102,11 +107,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005BA85B"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,9 +176,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -615,7 +615,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>La CNN 1D es el mejor control en salto reversible, desacople y cambio de fuente: los defectos sin estadístico cerrado evidente. Y en el escenario de DATO NUEVO —el frecuente, donde el control de vintage no puede ayudar— es el mejor control en 4 de las 7 familias. Aporta de forma real y MODESTA; no sustituye a ningún control explícito, y en dato nuevo lo es dentro de un campo débil (recalls de 0,10 a 0,76).</t>
+          <t>La CNN forma parte del banco de detectores, pero esta evaluación sintética no demuestra superioridad generalizable. Los mejores controles por familia se seleccionan sobre el mismo test y son resultados exploratorios; requieren validación externa y etiquetas reales.</t>
         </is>
       </c>
     </row>
@@ -634,12 +634,12 @@
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Qué NO aporta el machine learning</t>
+          <t>Qué no está demostrado sobre el machine learning</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>XGBoost como combinador de señales PIERDE contra la unión de controles con umbral propio, y en pérdida de precisión destruye un control que acierta el 100 %. «ML que apoya» sí; «ML que sustituye» no.</t>
+          <t>No se demuestra superioridad de CNN ni XGBoost. La FPR OOS de las configuraciones difiere y la comparación XGBoost-unión no está igualada en operación; hacen falta curvas de rendimiento y validación externa.</t>
         </is>
       </c>
     </row>
@@ -651,7 +651,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Solo son interpretables las comparaciones a la MISMA tasa de falsas alarmas. La hoja 3 compara control contra control a presupuesto común. La hoja 4 describe puntos de operación distintos y su diferencia de recall NO mide valor incremental.</t>
+          <t>Los umbrales se calibran con un objetivo nominal común en validación, pero la FPR observada en test difiere entre controles. Las comparaciones por familia son descriptivas y exploratorias; no identifican valor incremental de CNN o XGBoost.</t>
         </is>
       </c>
     </row>
@@ -663,7 +663,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>En Brent, |z|&gt;3 ocurre el 1.11% de las sesiones frente al 0.27% que predice una normal: 4,1 veces más. Un umbral 3σ no puede separar una cola real de mercado de un defecto de dato.</t>
+          <t>En Brent, |z|&gt;3 ocurre el 1.11% de las sesiones frente al 0.27% de referencia gaussiana. Es una estadística descriptiva estandarizada ex post, no un test de defectos ni evidencia de que 3σ distinga errores de mercado.</t>
         </is>
       </c>
     </row>
@@ -769,17 +769,17 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Recall a presupuesto común</t>
+          <t>Recall a objetivo nominal</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Comparar recalls solo tiene sentido si todos los controles operan a la MISMA carga de alarmas. Si no, el que más alerta parece el más sensible. Todo el Excel está medido así.</t>
+          <t>Los umbrales se fijan en una porción de validación limpia con un objetivo nominal del 5 %. La tasa realizada se mide en el test posterior y puede diferir por deriva y dependencia.</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>recall | FPR = 5 %</t>
+          <t>recall; FPR OOS aparte</t>
         </is>
       </c>
     </row>
@@ -808,7 +808,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Nivel de recall que alcanzaría un detector que alertase al azar al 5 %. En las tablas, las celdas en gris están en el azar: ese control NO ve esa familia.</t>
+          <t>Referencia aproximada para un detector aleatorio con prevalencia de alertas del 5 %. En tablas, las celdas en gris están en el azar: ese control NO ve esa familia.</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -897,7 +897,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Estrictamente cronológica, sin mezclar. Entrenamiento hasta 2018-12-31 (558 ventanas). Validación 2019-2023 (236). Test desde 2024-01-05 (124). La CNN se entrena en entrenamiento, el combinador XGBoost en validación y TODO se evalúa en test.</t>
+          <t>Estrictamente cronológica, sin mezclar. Entrenamiento hasta 2018-12-31 (558 ventanas). Validación 2019-2023 (236), separada en ajuste temprano y calibración posterior con purga por solapamiento. CNN y XGBoost se ajustan sin test; los umbrales se congelan antes de evaluar el bloque desde 2024-01-05 (124 ventanas).</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Gate conforme-adaptativo (Adaptive Conformal Inference). El umbral se calibra sobre tramos limpios de VALIDACIÓN y se reajusta en línea con la falsa alarma observada, sin suponer una forma de distribución — que es donde falla un 3σ paramétrico sobre estas colas. La garantía NO es incondicional: depende de la dependencia entre ventanas, del drift y del tamaño de la muestra de calibración, y aquí las ventanas solapan.</t>
+          <t>Umbral empírico de orden estadístico calibrado en un segmento tardío de validación, separado del ajuste por una purga de ventanas solapadas. Queda congelado antes del test. La FPR de test se informa sin feedback; no se reclama garantía conformal ni control bajo drift.</t>
         </is>
       </c>
     </row>
@@ -975,13 +975,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -995,6 +995,7 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1007,7 +1008,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Recall por control y familia, a presupuesto de falsas alarmas común (5%). Azar ≈ 0.048; en gris lo que está en el azar. «Reescribe historia» = el defecto altera datos ya publicados; «dato nuevo» = solo afecta a las sesiones recientes.</t>
+          <t>Recall por control y familia; objetivo nominal de calibración 5%, FPR de test observada y no igualada. Azar ≈ 0.048; en gris lo que está en el azar. «Reescribe historia» = el defecto altera datos ya publicados; «dato nuevo» = solo afecta a las sesiones recientes.</t>
         </is>
       </c>
     </row>
@@ -1029,83 +1030,88 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>FPR test</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>stale
 (reescribe)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>reversible_jump
 (reescribe)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>decoupling
 (reescribe)</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>lag1_calendar
 (reescribe)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>weekly_ffill
 (reescribe)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>source_switch
 (reescribe)</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>quantize
 (reescribe)</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>stale
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>reversible_jump
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>decoupling
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>lag1_calendar
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>weekly_ffill
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>source_switch
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>quantize
 (dato nuevo)</t>
@@ -1128,47 +1134,50 @@
           <t>retorno</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="E5" s="11" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="G5" s="10" t="n">
-        <v>0.089</v>
-      </c>
-      <c r="H5" s="10" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>0.056</v>
+      <c r="D5" s="9" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="E5" s="10" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="F5" s="11" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="G5" s="12" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="H5" s="12" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="I5" s="12" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="J5" s="12" t="n">
+        <v>0.438</v>
       </c>
       <c r="K5" s="10" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="M5" s="10" t="n">
-        <v>0.056</v>
+        <v>0.202</v>
+      </c>
+      <c r="L5" s="10" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="M5" s="11" t="n">
+        <v>0.866</v>
       </c>
       <c r="N5" s="10" t="n">
-        <v>0.081</v>
+        <v>0.231</v>
       </c>
       <c r="O5" s="10" t="n">
-        <v>0.056</v>
+        <v>0.234</v>
       </c>
       <c r="P5" s="10" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="Q5" s="10" t="n">
-        <v>0.056</v>
+        <v>0.194</v>
+      </c>
+      <c r="Q5" s="12" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="R5" s="10" t="n">
+        <v>0.199</v>
       </c>
     </row>
     <row r="6">
@@ -1187,47 +1196,50 @@
           <t>retorno</t>
         </is>
       </c>
-      <c r="D6" s="12" t="n">
-        <v>0.629</v>
+      <c r="D6" s="9" t="n">
+        <v>0.387</v>
       </c>
       <c r="E6" s="11" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="L6" s="11" t="n">
-        <v>0.425</v>
+        <v>1</v>
+      </c>
+      <c r="F6" s="11" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="G6" s="11" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="H6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="11" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="K6" s="12" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="L6" s="13" t="n">
+        <v>0.637</v>
       </c>
       <c r="M6" s="11" t="n">
-        <v>0.253</v>
+        <v>0.957</v>
       </c>
       <c r="N6" s="11" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="O6" s="10" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="P6" s="10" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Q6" s="13" t="n">
-        <v>0.04</v>
+        <v>0.844</v>
+      </c>
+      <c r="O6" s="11" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="P6" s="13" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q6" s="11" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R6" s="12" t="n">
+        <v>0.39</v>
       </c>
     </row>
     <row r="7">
@@ -1246,47 +1258,50 @@
           <t>retorno</t>
         </is>
       </c>
-      <c r="D7" s="12" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>0.793</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>0.839</v>
+      <c r="D7" s="9" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="E7" s="11" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="F7" s="11" t="n">
+        <v>0.925</v>
       </c>
       <c r="G7" s="11" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>0.57</v>
+        <v>0.984</v>
+      </c>
+      <c r="H7" s="11" t="n">
+        <v>0.753</v>
       </c>
       <c r="I7" s="11" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="L7" s="14" t="n">
-        <v>0.755</v>
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="J7" s="13" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K7" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L7" s="12" t="n">
+        <v>0.395</v>
       </c>
       <c r="M7" s="11" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="O7" s="10" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="P7" s="11" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="Q7" s="10" t="n">
-        <v>0.059</v>
+        <v>0.901</v>
+      </c>
+      <c r="N7" s="13" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="O7" s="13" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="P7" s="12" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="Q7" s="13" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="R7" s="12" t="n">
+        <v>0.285</v>
       </c>
     </row>
     <row r="8">
@@ -1305,46 +1320,49 @@
           <t>precio</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="13" t="n">
         <v>0.613</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="F8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="13" t="n">
+      <c r="G8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="13" t="n">
+      <c r="H8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="13" t="n">
+      <c r="I8" s="14" t="n">
         <v>0.027</v>
       </c>
-      <c r="I8" s="13" t="n">
+      <c r="J8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="K8" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="13" t="n">
+      <c r="L8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="L8" s="13" t="n">
+      <c r="M8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="13" t="n">
+      <c r="N8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="13" t="n">
+      <c r="O8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="13" t="n">
+      <c r="P8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="13" t="n">
+      <c r="Q8" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="13" t="n">
+      <c r="R8" s="14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1364,47 +1382,50 @@
           <t>canal</t>
         </is>
       </c>
-      <c r="D9" s="14" t="n">
+      <c r="D9" s="9" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="E9" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="12" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="F9" s="12" t="n">
+      <c r="F9" s="11" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="G9" s="11" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="H9" s="11" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="I9" s="11" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="J9" s="13" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K9" s="12" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L9" s="12" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="M9" s="11" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="N9" s="13" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="O9" s="13" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="P9" s="12" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="Q9" s="13" t="n">
         <v>0.656</v>
       </c>
-      <c r="G9" s="12" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="M9" s="11" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="N9" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O9" s="10" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="P9" s="10" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="Q9" s="13" t="n">
-        <v>0.048</v>
+      <c r="R9" s="12" t="n">
+        <v>0.282</v>
       </c>
     </row>
     <row r="10">
@@ -1423,47 +1444,50 @@
           <t>canal</t>
         </is>
       </c>
-      <c r="D10" s="14" t="n">
+      <c r="D10" s="9" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="E10" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="13" t="n">
-        <v>0.027</v>
-      </c>
       <c r="F10" s="10" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>0.876</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>0.048</v>
+        <v>0.062</v>
+      </c>
+      <c r="G10" s="10" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H10" s="10" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="I10" s="11" t="n">
+        <v>1</v>
       </c>
       <c r="J10" s="10" t="n">
-        <v>0.097</v>
+        <v>0.105</v>
       </c>
       <c r="K10" s="10" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="N10" s="13" t="n">
-        <v>0.008</v>
+        <v>0.212</v>
+      </c>
+      <c r="L10" s="12" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="M10" s="10" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="N10" s="10" t="n">
+        <v>0.054</v>
       </c>
       <c r="O10" s="10" t="n">
-        <v>0.102</v>
+        <v>0.073</v>
       </c>
       <c r="P10" s="10" t="n">
-        <v>0.051</v>
+        <v>0.18</v>
       </c>
       <c r="Q10" s="10" t="n">
-        <v>0.065</v>
+        <v>0.091</v>
+      </c>
+      <c r="R10" s="10" t="n">
+        <v>0.118</v>
       </c>
     </row>
     <row r="11">
@@ -1482,47 +1506,50 @@
           <t>canal</t>
         </is>
       </c>
-      <c r="D11" s="13" t="n">
+      <c r="D11" s="9" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="E11" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E11" s="12" t="n">
-        <v>0.6879999999999999</v>
-      </c>
       <c r="F11" s="13" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="H11" s="10" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="G11" s="10" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="H11" s="12" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="I11" s="10" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="J11" s="10" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K11" s="10" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="L11" s="10" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="M11" s="13" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="N11" s="10" t="n">
         <v>0.091</v>
       </c>
-      <c r="I11" s="10" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="M11" s="10" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="N11" s="10" t="n">
+      <c r="O11" s="10" t="n">
         <v>0.065</v>
       </c>
-      <c r="O11" s="13" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="P11" s="13" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="Q11" s="13" t="n">
-        <v>0.043</v>
+      <c r="P11" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q11" s="10" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R11" s="10" t="n">
+        <v>0.056</v>
       </c>
     </row>
     <row r="12">
@@ -1541,47 +1568,50 @@
           <t>canal</t>
         </is>
       </c>
-      <c r="D12" s="13" t="n">
+      <c r="D12" s="9" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="E12" s="14" t="n">
         <v>0</v>
       </c>
-      <c r="E12" s="11" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>0.148</v>
+      <c r="F12" s="12" t="n">
+        <v>0.454</v>
       </c>
       <c r="G12" s="10" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="H12" s="11" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>0.14</v>
+        <v>0.196</v>
+      </c>
+      <c r="H12" s="10" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="I12" s="12" t="n">
+        <v>0.366</v>
       </c>
       <c r="J12" s="10" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="M12" s="10" t="n">
-        <v>0.054</v>
+        <v>0.167</v>
+      </c>
+      <c r="K12" s="10" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="L12" s="10" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="M12" s="12" t="n">
+        <v>0.409</v>
       </c>
       <c r="N12" s="10" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>0.038</v>
+        <v>0.091</v>
+      </c>
+      <c r="O12" s="10" t="n">
+        <v>0.089</v>
       </c>
       <c r="P12" s="10" t="n">
-        <v>0.159</v>
+        <v>0.078</v>
       </c>
       <c r="Q12" s="10" t="n">
-        <v>0.062</v>
+        <v>0.226</v>
+      </c>
+      <c r="R12" s="10" t="n">
+        <v>0.089</v>
       </c>
     </row>
     <row r="13">
@@ -1600,47 +1630,50 @@
           <t>vintage</t>
         </is>
       </c>
-      <c r="D13" s="14" t="n">
+      <c r="D13" s="9" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="E13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="12" t="n">
-        <v>0.747</v>
-      </c>
-      <c r="F13" s="14" t="n">
+      <c r="F13" s="11" t="n">
+        <v>0.874</v>
+      </c>
+      <c r="G13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="G13" s="14" t="n">
+      <c r="H13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="14" t="n">
+      <c r="I13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="14" t="n">
+      <c r="J13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="14" t="n">
+      <c r="K13" s="11" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="P13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="Q13" s="13" t="n">
-        <v>0.048</v>
+      <c r="L13" s="12" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="M13" s="12" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="N13" s="12" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="O13" s="12" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="P13" s="12" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="Q13" s="12" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="R13" s="12" t="n">
+        <v>0.468</v>
       </c>
     </row>
   </sheetData>
@@ -1677,7 +1710,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ATENCIÓN AL LEER ESTA HOJA: cada configuración opera a una tasa de falsas alarmas DISTINTA, así que la diferencia de recall entre filas NO aísla el valor incremental de ninguna capa. Se incluye porque describe el punto de operación de cada configuración, no como medida de mejora. La comparación que sí es válida —control contra control a presupuesto común— está en la hoja 3.</t>
+          <t>Los umbrales se calibran con el mismo objetivo nominal en validación, pero la FPR realizada en test difiere. Las diferencias de recall son descriptivas y no aíslan el valor incremental de ninguna capa. Este benchmark mide controles en paralelo; no valida un router secuencial.</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1727,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Falsas alarmas medidas</t>
+          <t>FPR observada en test</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1720,13 +1753,13 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.032</v>
+        <v>0.194</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.074</v>
+        <v>0.371</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.032</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="6">
@@ -1741,13 +1774,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.081</v>
+        <v>0.758</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.579</v>
+        <v>0.946</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.078</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="7">
@@ -1762,29 +1795,29 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.083</v>
+        <v>0.774</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.606</v>
+        <v>0.951</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.083</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>Aportación marginal de la CNN sobre el banco</t>
+          <t>Diferencia descriptiva: banco con CNN menos banco sin CNN</t>
         </is>
       </c>
       <c r="D9" s="15" t="n">
-        <v>0.026</v>
+        <v>0.006</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>Esa diferencia marginal es la única de esta hoja medida entre dos configuraciones a falsas alarmas casi iguales (0,081 y 0,083), así que es la única interpretable como aportación. Las demás filas difieren también en punto de operación.</t>
+          <t>Diferencia exploratoria post hoc sobre el mismo test; no es una estimación confirmatoria de aportación incremental. Requiere test externo y protocolo preespecificado.</t>
         </is>
       </c>
     </row>
@@ -1823,7 +1856,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Qué es cada familia de defecto y qué control la cubre mejor.</t>
+          <t>Mejor control observado por familia, selección post hoc en el mismo test; lectura exploratoria.</t>
         </is>
       </c>
     </row>
@@ -1880,11 +1913,11 @@
       </c>
       <c r="E5" s="9" t="inlineStr">
         <is>
-          <t>canal_oscilacion</t>
+          <t>retorno_cross_asset</t>
         </is>
       </c>
       <c r="F5" s="18" t="n">
-        <v>0.145</v>
+        <v>0.637</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
@@ -1900,19 +1933,19 @@
       </c>
       <c r="C6" s="9" t="inlineStr">
         <is>
-          <t>retorno_cnn</t>
+          <t>retorno_cross_asset</t>
         </is>
       </c>
       <c r="D6" s="17" t="n">
-        <v>0.793</v>
+        <v>0.968</v>
       </c>
       <c r="E6" s="9" t="inlineStr">
         <is>
-          <t>retorno_cnn</t>
+          <t>retorno_cross_asset</t>
         </is>
       </c>
       <c r="F6" s="17" t="n">
-        <v>0.755</v>
+        <v>0.957</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -1936,11 +1969,11 @@
       </c>
       <c r="E7" s="9" t="inlineStr">
         <is>
-          <t>retorno_cnn</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>0.366</v>
+          <t>retorno_cross_asset</t>
+        </is>
+      </c>
+      <c r="F7" s="17" t="n">
+        <v>0.844</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
@@ -1956,7 +1989,7 @@
       </c>
       <c r="C8" s="9" t="inlineStr">
         <is>
-          <t>vintage_discrepancia</t>
+          <t>retorno_cross_asset</t>
         </is>
       </c>
       <c r="D8" s="17" t="n">
@@ -1967,8 +2000,8 @@
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="F8" s="19" t="n">
-        <v>0.282</v>
+      <c r="F8" s="17" t="n">
+        <v>0.839</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -1984,7 +2017,7 @@
       </c>
       <c r="C9" s="9" t="inlineStr">
         <is>
-          <t>vintage_discrepancia</t>
+          <t>canal_oscilacion</t>
         </is>
       </c>
       <c r="D9" s="17" t="n">
@@ -1992,11 +2025,11 @@
       </c>
       <c r="E9" s="9" t="inlineStr">
         <is>
-          <t>retorno_cnn</t>
+          <t>retorno_cross_asset</t>
         </is>
       </c>
       <c r="F9" s="18" t="n">
-        <v>0.105</v>
+        <v>0.53</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
@@ -2020,11 +2053,11 @@
       </c>
       <c r="E10" s="9" t="inlineStr">
         <is>
-          <t>retorno_cnn</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.309</v>
+          <t>retorno_cross_asset</t>
+        </is>
+      </c>
+      <c r="F10" s="17" t="n">
+        <v>0.75</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
@@ -2048,11 +2081,11 @@
       </c>
       <c r="E11" s="9" t="inlineStr">
         <is>
-          <t>canal_oscilacion</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>0.065</v>
+          <t>vintage_discrepancia</t>
+        </is>
+      </c>
+      <c r="F11" s="19" t="n">
+        <v>0.468</v>
       </c>
     </row>
   </sheetData>
@@ -2246,14 +2279,14 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Cada familia de defecto la cubre bien un control distinto y varias las ve uno solo. Medido con defectos de verdad conocida sobre test temporal y presupuesto de falsas alarmas común. Pendiente de auditoría cruzada.</t>
+          <t>Los controles muestran perfiles de cobertura distintos y varias familias quedan cubiertas por un único control en este test. Medido con defectos de verdad conocida sobre test temporal y presupuesto de falsas alarmas nominal calibrado en validación; la FPR se mide en test y puede diferir. Pendiente de auditoría cruzada.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Calibración conforme del umbral</t>
+          <t>Calibración empírica del umbral</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -2263,7 +2296,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>El gate conforme-adaptativo alcanza el presupuesto de falsas alarmas fijado sin suponer una forma de distribución. Un umbral paramétrico 3σ no lo consigue sobre estas colas.</t>
+          <t>Se congela un umbral empírico usando un bloque de validación separado y purgado. No se reclama garantía conformal ni control de FPR bajo drift.</t>
         </is>
       </c>
     </row>
@@ -2292,12 +2325,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>🟡 provisional</t>
+          <t>🟡 exploratorio</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Es el mejor control en las familias sin estadístico cerrado evidente, y el que más cubre en el escenario de dato nuevo. La mejora sobre el banco completo es real y modesta.</t>
+          <t>La evaluación sintética no demuestra superioridad generalizable. La selección de ganadores se hace sobre el mismo test; hacen falta prueba externa y etiquetas reales.</t>
         </is>
       </c>
     </row>
@@ -2307,14 +2340,14 @@
           <t>XGBoost como combinador</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>🟡 provisional · resultado negativo</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>🟡 no concluyente</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Rinde por debajo de la unión de los mismos controles con umbral propio, y diluye los controles que resuelven una familia de forma exacta. Se publica como negativo.</t>
+          <t>Su recall y el de la unión se observan con FPR OOS distintas. No se puede afirmar que uno supere al otro sin comparar a un mismo punto de operación o sobre curvas ROC/PR.</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2382,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2433,34 +2466,46 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>FPR no idénticas</t>
+          <t>FPR observada no igualada</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Gate A opera a 0,032 y Gate B a 0,083 de falsas alarmas: la comparación es generosa en alarmas para Gate B.</t>
+          <t>La FPR de test puede diferir entre controles pese a calibrar umbrales al mismo objetivo nominal; no interpretar recall como comparación a operación idéntica.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Un solo activo y un solo panel</t>
+          <t>Resolución de calibración</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Todo el banco se ha medido sobre Brent y sus cuatro pares. La transferencia a otras asset classes NO está demostrada.</t>
+          <t>El bloque de calibración es finito. La cuota de Bonferroni por control puede quedar por debajo de una observación (1/n), en cuyo caso el umbral empírico se sitúa en el máximo de calibración y no puede realizar exactamente el objetivo nominal.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>Un solo activo y un solo panel</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Todo el banco se ha medido sobre Brent y sus cuatro pares. La transferencia a otras asset classes NO está demostrada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>Capital</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>No se reporta ninguna cifra de capital. Sería k·VaR con el semáforo de Basilea, pero exigiría cartera real, correlaciones, diversificación entre mesas, específico y default, PLA por mesa, NMRF y suelo SA.</t>
         </is>

--- a/results/reports/dq_entregables/resultados_dq.xlsx
+++ b/results/reports/dq_entregables/resultados_dq.xlsx
@@ -9,12 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Métricas y protocolo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Cobertura" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Gate A vs Gate B" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Familias" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Modelos aguas abajo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Estado" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 Limitaciones" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Punto de operación" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Cobertura" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Gate A vs Gate B" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Familias" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Modelos aguas abajo" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 Estado" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9 Limitaciones" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -136,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -156,6 +157,15 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -675,7 +685,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>No se da ninguna cifra de capital. No se demuestra transferencia a otras asset classes. No se afirma prevalencia real de defectos. Ver hoja 8.</t>
+          <t>No se da ninguna cifra de capital. No se demuestra transferencia a otras asset classes. No se afirma prevalencia real de defectos. Ver hoja 9.</t>
         </is>
       </c>
     </row>
@@ -752,12 +762,12 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>FPR (tasa de falsas alarmas)</t>
+          <t>FPR realizada</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>De los tramos LIMPIOS, qué fracción levantó alerta igualmente. Es el coste operativo: cada falsa alarma es trabajo de revisión que no encuentra nada. Objetivo fijado: 5 %.</t>
+          <t>De los tramos LIMPIOS, qué fracción levantó alerta igualmente. Es el coste operativo: cada falsa alarma es trabajo de revisión que no encuentra nada. NO se promete un objetivo nominal, porque no se cumple fuera de muestra: se DECLARA la medida. Ver la hoja de punto de operación.</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -970,6 +980,200 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>3 Punto de operación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>LA HOJA QUE HAY QUE LEER PARA DIMENSIONAR LA REVISIÓN. El gate no promete una tasa nominal de falsas alarmas, porque no se cumple fuera de muestra: declara la medida. Elige la fila por capacidad de revisión disponible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>α nominal pedido</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>FPR REALIZADA</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>dispersión</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>exceso sobre nominal</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>recall medio</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>± 0.004</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>16.7x</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.605</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>± 0.004</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>8.3x</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.608</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>± 0.004</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>5.0x</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.616</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>± 0.004</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>2.3x</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.646</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>± 0.011</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>2.0x</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>SUELO MEDIDO: el gate no baja de 0.083 de ventanas limpias marcadas. Pedir un α de 0,005 o de 0,010 da exactamente lo mismo, así que dimensionar la revisión suponiendo un 5 % o un 1 % es dimensionar mal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Por encima del suelo el intercambio es real y suave: más carga de revisión compra más cobertura. El punto se elige por capacidad disponible, no por un número de referencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>El exceso sobre el nominal tiene dos causas medidas. La resolución de la muestra de calibración ya está corregida ampliando la ventana. La que queda es deriva: cada control realiza ~2,6 veces su tasa nominal porque el tramo reciente no predice la cola del siguiente. Esa es la que fija el suelo y no se arregla repartiendo mejor.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1001,7 +1205,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>3 Cobertura</t>
+          <t>4 Cobertura</t>
         </is>
       </c>
     </row>
@@ -1119,560 +1323,560 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>retorno_3sigma</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Gate A</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>retorno</t>
         </is>
       </c>
-      <c r="D5" s="9" t="n">
+      <c r="D5" s="12" t="n">
         <v>0.194</v>
       </c>
-      <c r="E5" s="10" t="n">
+      <c r="E5" s="13" t="n">
         <v>0.194</v>
       </c>
-      <c r="F5" s="11" t="n">
+      <c r="F5" s="14" t="n">
         <v>0.879</v>
       </c>
-      <c r="G5" s="12" t="n">
+      <c r="G5" s="15" t="n">
         <v>0.409</v>
       </c>
-      <c r="H5" s="12" t="n">
+      <c r="H5" s="15" t="n">
         <v>0.347</v>
       </c>
-      <c r="I5" s="12" t="n">
+      <c r="I5" s="15" t="n">
         <v>0.374</v>
       </c>
-      <c r="J5" s="12" t="n">
+      <c r="J5" s="15" t="n">
         <v>0.438</v>
       </c>
-      <c r="K5" s="10" t="n">
+      <c r="K5" s="13" t="n">
         <v>0.202</v>
       </c>
-      <c r="L5" s="10" t="n">
+      <c r="L5" s="13" t="n">
         <v>0.194</v>
       </c>
-      <c r="M5" s="11" t="n">
+      <c r="M5" s="14" t="n">
         <v>0.866</v>
       </c>
-      <c r="N5" s="10" t="n">
+      <c r="N5" s="13" t="n">
         <v>0.231</v>
       </c>
-      <c r="O5" s="10" t="n">
+      <c r="O5" s="13" t="n">
         <v>0.234</v>
       </c>
-      <c r="P5" s="10" t="n">
+      <c r="P5" s="13" t="n">
         <v>0.194</v>
       </c>
-      <c r="Q5" s="12" t="n">
+      <c r="Q5" s="15" t="n">
         <v>0.433</v>
       </c>
-      <c r="R5" s="10" t="n">
+      <c r="R5" s="13" t="n">
         <v>0.199</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="12" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>retorno</t>
         </is>
       </c>
-      <c r="D6" s="9" t="n">
+      <c r="D6" s="12" t="n">
         <v>0.387</v>
       </c>
-      <c r="E6" s="11" t="n">
+      <c r="E6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F6" s="11" t="n">
+      <c r="F6" s="14" t="n">
         <v>0.968</v>
       </c>
-      <c r="G6" s="11" t="n">
+      <c r="G6" s="14" t="n">
         <v>0.997</v>
       </c>
-      <c r="H6" s="11" t="n">
+      <c r="H6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="I6" s="11" t="n">
+      <c r="I6" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="J6" s="11" t="n">
+      <c r="J6" s="14" t="n">
         <v>0.782</v>
       </c>
-      <c r="K6" s="12" t="n">
+      <c r="K6" s="15" t="n">
         <v>0.403</v>
       </c>
-      <c r="L6" s="13" t="n">
+      <c r="L6" s="16" t="n">
         <v>0.637</v>
       </c>
-      <c r="M6" s="11" t="n">
+      <c r="M6" s="14" t="n">
         <v>0.957</v>
       </c>
-      <c r="N6" s="11" t="n">
+      <c r="N6" s="14" t="n">
         <v>0.844</v>
       </c>
-      <c r="O6" s="11" t="n">
+      <c r="O6" s="14" t="n">
         <v>0.839</v>
       </c>
-      <c r="P6" s="13" t="n">
+      <c r="P6" s="16" t="n">
         <v>0.53</v>
       </c>
-      <c r="Q6" s="11" t="n">
+      <c r="Q6" s="14" t="n">
         <v>0.75</v>
       </c>
-      <c r="R6" s="12" t="n">
+      <c r="R6" s="15" t="n">
         <v>0.39</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>retorno_cnn</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="12" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>retorno</t>
         </is>
       </c>
-      <c r="D7" s="9" t="n">
+      <c r="D7" s="12" t="n">
         <v>0.282</v>
       </c>
-      <c r="E7" s="11" t="n">
+      <c r="E7" s="14" t="n">
         <v>0.903</v>
       </c>
-      <c r="F7" s="11" t="n">
+      <c r="F7" s="14" t="n">
         <v>0.925</v>
       </c>
-      <c r="G7" s="11" t="n">
+      <c r="G7" s="14" t="n">
         <v>0.984</v>
       </c>
-      <c r="H7" s="11" t="n">
+      <c r="H7" s="14" t="n">
         <v>0.753</v>
       </c>
-      <c r="I7" s="11" t="n">
+      <c r="I7" s="14" t="n">
         <v>0.8090000000000001</v>
       </c>
-      <c r="J7" s="13" t="n">
+      <c r="J7" s="16" t="n">
         <v>0.594</v>
       </c>
-      <c r="K7" s="12" t="n">
+      <c r="K7" s="15" t="n">
         <v>0.28</v>
       </c>
-      <c r="L7" s="12" t="n">
+      <c r="L7" s="15" t="n">
         <v>0.395</v>
       </c>
-      <c r="M7" s="11" t="n">
+      <c r="M7" s="14" t="n">
         <v>0.901</v>
       </c>
-      <c r="N7" s="13" t="n">
+      <c r="N7" s="16" t="n">
         <v>0.629</v>
       </c>
-      <c r="O7" s="13" t="n">
+      <c r="O7" s="16" t="n">
         <v>0.503</v>
       </c>
-      <c r="P7" s="12" t="n">
+      <c r="P7" s="15" t="n">
         <v>0.341</v>
       </c>
-      <c r="Q7" s="13" t="n">
+      <c r="Q7" s="16" t="n">
         <v>0.586</v>
       </c>
-      <c r="R7" s="12" t="n">
+      <c r="R7" s="15" t="n">
         <v>0.285</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>precio_reticula</t>
         </is>
       </c>
-      <c r="B8" s="9" t="inlineStr">
+      <c r="B8" s="12" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>precio</t>
         </is>
       </c>
-      <c r="D8" s="9" t="n">
+      <c r="D8" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="E8" s="13" t="n">
+      <c r="E8" s="16" t="n">
         <v>0.613</v>
       </c>
-      <c r="F8" s="14" t="n">
+      <c r="F8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="G8" s="14" t="n">
+      <c r="G8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="H8" s="14" t="n">
+      <c r="H8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="I8" s="14" t="n">
+      <c r="I8" s="17" t="n">
         <v>0.027</v>
       </c>
-      <c r="J8" s="14" t="n">
+      <c r="J8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="K8" s="11" t="n">
+      <c r="K8" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="L8" s="14" t="n">
+      <c r="L8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="M8" s="14" t="n">
+      <c r="M8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="N8" s="14" t="n">
+      <c r="N8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="O8" s="14" t="n">
+      <c r="O8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="P8" s="14" t="n">
+      <c r="P8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="Q8" s="14" t="n">
+      <c r="Q8" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="R8" s="14" t="n">
+      <c r="R8" s="17" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>canal_coherencia</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B9" s="12" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D9" s="9" t="n">
+      <c r="D9" s="12" t="n">
         <v>0.282</v>
       </c>
-      <c r="E9" s="11" t="n">
+      <c r="E9" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="11" t="n">
+      <c r="F9" s="14" t="n">
         <v>0.895</v>
       </c>
-      <c r="G9" s="11" t="n">
+      <c r="G9" s="14" t="n">
         <v>0.968</v>
       </c>
-      <c r="H9" s="11" t="n">
+      <c r="H9" s="14" t="n">
         <v>0.992</v>
       </c>
-      <c r="I9" s="11" t="n">
+      <c r="I9" s="14" t="n">
         <v>0.962</v>
       </c>
-      <c r="J9" s="13" t="n">
+      <c r="J9" s="16" t="n">
         <v>0.637</v>
       </c>
-      <c r="K9" s="12" t="n">
+      <c r="K9" s="15" t="n">
         <v>0.28</v>
       </c>
-      <c r="L9" s="12" t="n">
+      <c r="L9" s="15" t="n">
         <v>0.476</v>
       </c>
-      <c r="M9" s="11" t="n">
+      <c r="M9" s="14" t="n">
         <v>0.903</v>
       </c>
-      <c r="N9" s="13" t="n">
+      <c r="N9" s="16" t="n">
         <v>0.6830000000000001</v>
       </c>
-      <c r="O9" s="13" t="n">
+      <c r="O9" s="16" t="n">
         <v>0.669</v>
       </c>
-      <c r="P9" s="12" t="n">
+      <c r="P9" s="15" t="n">
         <v>0.358</v>
       </c>
-      <c r="Q9" s="13" t="n">
+      <c r="Q9" s="16" t="n">
         <v>0.656</v>
       </c>
-      <c r="R9" s="12" t="n">
+      <c r="R9" s="15" t="n">
         <v>0.282</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>canal_oscilacion</t>
         </is>
       </c>
-      <c r="B10" s="9" t="inlineStr">
+      <c r="B10" s="12" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D10" s="9" t="n">
+      <c r="D10" s="12" t="n">
         <v>0.097</v>
       </c>
-      <c r="E10" s="11" t="n">
+      <c r="E10" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="10" t="n">
+      <c r="F10" s="13" t="n">
         <v>0.062</v>
       </c>
-      <c r="G10" s="10" t="n">
+      <c r="G10" s="13" t="n">
         <v>0.075</v>
       </c>
-      <c r="H10" s="10" t="n">
+      <c r="H10" s="13" t="n">
         <v>0.073</v>
       </c>
-      <c r="I10" s="11" t="n">
+      <c r="I10" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="J10" s="10" t="n">
+      <c r="J10" s="13" t="n">
         <v>0.105</v>
       </c>
-      <c r="K10" s="10" t="n">
+      <c r="K10" s="13" t="n">
         <v>0.212</v>
       </c>
-      <c r="L10" s="12" t="n">
+      <c r="L10" s="15" t="n">
         <v>0.258</v>
       </c>
-      <c r="M10" s="10" t="n">
+      <c r="M10" s="13" t="n">
         <v>0.062</v>
       </c>
-      <c r="N10" s="10" t="n">
+      <c r="N10" s="13" t="n">
         <v>0.054</v>
       </c>
-      <c r="O10" s="10" t="n">
+      <c r="O10" s="13" t="n">
         <v>0.073</v>
       </c>
-      <c r="P10" s="10" t="n">
+      <c r="P10" s="13" t="n">
         <v>0.18</v>
       </c>
-      <c r="Q10" s="10" t="n">
+      <c r="Q10" s="13" t="n">
         <v>0.091</v>
       </c>
-      <c r="R10" s="10" t="n">
+      <c r="R10" s="13" t="n">
         <v>0.118</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>canal_ruptura</t>
         </is>
       </c>
-      <c r="B11" s="9" t="inlineStr">
+      <c r="B11" s="12" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D11" s="9" t="n">
+      <c r="D11" s="12" t="n">
         <v>0.065</v>
       </c>
-      <c r="E11" s="14" t="n">
+      <c r="E11" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="13" t="n">
+      <c r="F11" s="16" t="n">
         <v>0.742</v>
       </c>
-      <c r="G11" s="10" t="n">
+      <c r="G11" s="13" t="n">
         <v>0.078</v>
       </c>
-      <c r="H11" s="12" t="n">
+      <c r="H11" s="15" t="n">
         <v>0.282</v>
       </c>
-      <c r="I11" s="10" t="n">
+      <c r="I11" s="13" t="n">
         <v>0.102</v>
       </c>
-      <c r="J11" s="10" t="n">
+      <c r="J11" s="13" t="n">
         <v>0.11</v>
       </c>
-      <c r="K11" s="10" t="n">
+      <c r="K11" s="13" t="n">
         <v>0.062</v>
       </c>
-      <c r="L11" s="10" t="n">
+      <c r="L11" s="13" t="n">
         <v>0.073</v>
       </c>
-      <c r="M11" s="13" t="n">
+      <c r="M11" s="16" t="n">
         <v>0.715</v>
       </c>
-      <c r="N11" s="10" t="n">
+      <c r="N11" s="13" t="n">
         <v>0.091</v>
       </c>
-      <c r="O11" s="10" t="n">
+      <c r="O11" s="13" t="n">
         <v>0.065</v>
       </c>
-      <c r="P11" s="10" t="n">
+      <c r="P11" s="13" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="Q11" s="10" t="n">
+      <c r="Q11" s="13" t="n">
         <v>0.07000000000000001</v>
       </c>
-      <c r="R11" s="10" t="n">
+      <c r="R11" s="13" t="n">
         <v>0.056</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
         <is>
           <t>canal_geometria</t>
         </is>
       </c>
-      <c r="B12" s="9" t="inlineStr">
+      <c r="B12" s="12" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>canal</t>
         </is>
       </c>
-      <c r="D12" s="9" t="n">
+      <c r="D12" s="12" t="n">
         <v>0.089</v>
       </c>
-      <c r="E12" s="14" t="n">
+      <c r="E12" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="12" t="n">
+      <c r="F12" s="15" t="n">
         <v>0.454</v>
       </c>
-      <c r="G12" s="10" t="n">
+      <c r="G12" s="13" t="n">
         <v>0.196</v>
       </c>
-      <c r="H12" s="10" t="n">
+      <c r="H12" s="13" t="n">
         <v>0.153</v>
       </c>
-      <c r="I12" s="12" t="n">
+      <c r="I12" s="15" t="n">
         <v>0.366</v>
       </c>
-      <c r="J12" s="10" t="n">
+      <c r="J12" s="13" t="n">
         <v>0.167</v>
       </c>
-      <c r="K12" s="10" t="n">
+      <c r="K12" s="13" t="n">
         <v>0.094</v>
       </c>
-      <c r="L12" s="10" t="n">
+      <c r="L12" s="13" t="n">
         <v>0.097</v>
       </c>
-      <c r="M12" s="12" t="n">
+      <c r="M12" s="15" t="n">
         <v>0.409</v>
       </c>
-      <c r="N12" s="10" t="n">
+      <c r="N12" s="13" t="n">
         <v>0.091</v>
       </c>
-      <c r="O12" s="10" t="n">
+      <c r="O12" s="13" t="n">
         <v>0.089</v>
       </c>
-      <c r="P12" s="10" t="n">
+      <c r="P12" s="13" t="n">
         <v>0.078</v>
       </c>
-      <c r="Q12" s="10" t="n">
+      <c r="Q12" s="13" t="n">
         <v>0.226</v>
       </c>
-      <c r="R12" s="10" t="n">
+      <c r="R12" s="13" t="n">
         <v>0.089</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="B13" s="9" t="inlineStr">
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>vintage</t>
         </is>
       </c>
-      <c r="D13" s="9" t="n">
+      <c r="D13" s="12" t="n">
         <v>0.468</v>
       </c>
-      <c r="E13" s="11" t="n">
+      <c r="E13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="F13" s="11" t="n">
+      <c r="F13" s="14" t="n">
         <v>0.874</v>
       </c>
-      <c r="G13" s="11" t="n">
+      <c r="G13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="H13" s="11" t="n">
+      <c r="H13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="I13" s="11" t="n">
+      <c r="I13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="J13" s="11" t="n">
+      <c r="J13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="11" t="n">
+      <c r="K13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="L13" s="12" t="n">
+      <c r="L13" s="15" t="n">
         <v>0.468</v>
       </c>
-      <c r="M13" s="12" t="n">
+      <c r="M13" s="15" t="n">
         <v>0.468</v>
       </c>
-      <c r="N13" s="12" t="n">
+      <c r="N13" s="15" t="n">
         <v>0.468</v>
       </c>
-      <c r="O13" s="12" t="n">
+      <c r="O13" s="15" t="n">
         <v>0.468</v>
       </c>
-      <c r="P13" s="12" t="n">
+      <c r="P13" s="15" t="n">
         <v>0.468</v>
       </c>
-      <c r="Q13" s="12" t="n">
+      <c r="Q13" s="15" t="n">
         <v>0.468</v>
       </c>
-      <c r="R13" s="12" t="n">
+      <c r="R13" s="15" t="n">
         <v>0.468</v>
       </c>
     </row>
@@ -1684,7 +1888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1703,7 +1907,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>4 Gate A vs Gate B</t>
+          <t>5 Gate A vs Gate B</t>
         </is>
       </c>
     </row>
@@ -1805,17 +2009,17 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
+      <c r="A9" s="18" t="inlineStr">
         <is>
           <t>Diferencia descriptiva: banco con CNN menos banco sin CNN</t>
         </is>
       </c>
-      <c r="D9" s="15" t="n">
+      <c r="D9" s="18" t="n">
         <v>0.006</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Diferencia exploratoria post hoc sobre el mismo test; no es una estimación confirmatoria de aportación incremental. Requiere test externo y protocolo preespecificado.</t>
         </is>
@@ -1829,7 +2033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1849,7 +2053,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5 Familias</t>
+          <t>6 Familias</t>
         </is>
       </c>
     </row>
@@ -1893,7 +2097,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>stale</t>
         </is>
@@ -1903,25 +2107,25 @@
           <t>Cotización repetida: el precio deja de moverse (check TRIM de ≥20 ceros).</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>canal_coherencia</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="21" t="n">
         <v>0.637</v>
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
         <is>
           <t>reversible_jump</t>
         </is>
@@ -1931,25 +2135,25 @@
           <t>Tick erróneo que revierte al día siguiente.</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="D6" s="17" t="n">
+      <c r="D6" s="20" t="n">
         <v>0.968</v>
       </c>
-      <c r="E6" s="9" t="inlineStr">
+      <c r="E6" s="12" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="F6" s="17" t="n">
+      <c r="F6" s="20" t="n">
         <v>0.957</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>decoupling</t>
         </is>
@@ -1959,25 +2163,25 @@
           <t>Desalineación de fechas de varias sesiones frente a los pares.</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D7" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="9" t="inlineStr">
+      <c r="E7" s="12" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="F7" s="17" t="n">
+      <c r="F7" s="20" t="n">
         <v>0.844</v>
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
         <is>
           <t>lag1_calendar</t>
         </is>
@@ -1987,25 +2191,25 @@
           <t>Desfase de UNA sesión. Es la forma del defecto real de EURUSD de 2008.</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
+      <c r="D8" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E8" s="9" t="inlineStr">
+      <c r="E8" s="12" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="F8" s="17" t="n">
+      <c r="F8" s="20" t="n">
         <v>0.839</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
         <is>
           <t>weekly_ffill</t>
         </is>
@@ -2015,25 +2219,25 @@
           <t>Fuente semanal propagada a diario: el precio solo cambia 1 de cada 5 días.</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>canal_oscilacion</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n">
+      <c r="D9" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E9" s="9" t="inlineStr">
+      <c r="E9" s="12" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="21" t="n">
         <v>0.53</v>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>source_switch</t>
         </is>
@@ -2043,25 +2247,25 @@
           <t>Empalme de proveedores: salto de nivel a mitad de tramo sin corregir.</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D10" s="17" t="n">
+      <c r="D10" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E10" s="9" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
         <is>
           <t>retorno_cross_asset</t>
         </is>
       </c>
-      <c r="F10" s="17" t="n">
+      <c r="F10" s="20" t="n">
         <v>0.75</v>
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
         <is>
           <t>quantize</t>
         </is>
@@ -2071,20 +2275,20 @@
           <t>Pérdida de precisión del feed: la cotización se trunca a menos decimales.</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>precio_reticula</t>
         </is>
       </c>
-      <c r="D11" s="17" t="n">
+      <c r="D11" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="9" t="inlineStr">
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="F11" s="19" t="n">
+      <c r="F11" s="22" t="n">
         <v>0.468</v>
       </c>
     </row>
@@ -2096,7 +2300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2114,7 +2318,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>6 Modelos aguas abajo</t>
+          <t>7 Modelos aguas abajo</t>
         </is>
       </c>
     </row>
@@ -2153,7 +2357,7 @@
           <t>VaR FHS-EWMA condicional a volatilidad</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Supera el backtest</t>
         </is>
@@ -2175,7 +2379,7 @@
           <t>Supervivencia del canal · XGB-AFT</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Supera el backtest</t>
         </is>
@@ -2197,7 +2401,7 @@
           <t>Detección de canal · CNN EfficientNet</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Pasa como clasificador, no como estrategia</t>
         </is>
@@ -2221,7 +2425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2238,7 +2442,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>7 Estado</t>
+          <t>8 Estado</t>
         </is>
       </c>
     </row>
@@ -2376,7 +2580,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2392,7 +2596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>8 Limitaciones</t>
+          <t>9 Limitaciones</t>
         </is>
       </c>
     </row>

--- a/results/reports/dq_entregables/resultados_dq.xlsx
+++ b/results/reports/dq_entregables/resultados_dq.xlsx
@@ -9,12 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="1 Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="2 Métricas y protocolo" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Cobertura" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Gate A vs Gate B" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Familias" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Modelos aguas abajo" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Estado" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 Limitaciones" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="3 Punto de operación" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="4 Cobertura" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="5 Gate A vs Gate B" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="6 Familias" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="7 Modelos aguas abajo" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="8 Estado" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="9 Limitaciones" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -91,6 +92,11 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="005BA85B"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00C7E3BE"/>
       </patternFill>
     </fill>
@@ -102,11 +108,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00EDEDED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="005BA85B"/>
       </patternFill>
     </fill>
   </fills>
@@ -136,7 +137,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -158,6 +159,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
@@ -176,9 +186,9 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -615,7 +625,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>La CNN 1D es el mejor control en salto reversible, desacople y cambio de fuente: los defectos sin estadístico cerrado evidente. Y en el escenario de DATO NUEVO —el frecuente, donde el control de vintage no puede ayudar— es el mejor control en 4 de las 7 familias. Aporta de forma real y MODESTA; no sustituye a ningún control explícito, y en dato nuevo lo es dentro de un campo débil (recalls de 0,10 a 0,76).</t>
+          <t>La CNN forma parte del banco de detectores, pero esta evaluación sintética no demuestra superioridad generalizable. Los mejores controles por familia se seleccionan sobre el mismo test y son resultados exploratorios; requieren validación externa y etiquetas reales.</t>
         </is>
       </c>
     </row>
@@ -634,12 +644,12 @@
     <row r="9" ht="46" customHeight="1">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Qué NO aporta el machine learning</t>
+          <t>Qué no está demostrado sobre el machine learning</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>XGBoost como combinador de señales PIERDE contra la unión de controles con umbral propio, y en pérdida de precisión destruye un control que acierta el 100 %. «ML que apoya» sí; «ML que sustituye» no.</t>
+          <t>No se demuestra superioridad de CNN ni XGBoost. La FPR OOS de las configuraciones difiere y la comparación XGBoost-unión no está igualada en operación; hacen falta curvas de rendimiento y validación externa.</t>
         </is>
       </c>
     </row>
@@ -651,7 +661,7 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Solo son interpretables las comparaciones a la MISMA tasa de falsas alarmas. La hoja 3 compara control contra control a presupuesto común. La hoja 4 describe puntos de operación distintos y su diferencia de recall NO mide valor incremental.</t>
+          <t>Los umbrales se calibran con un objetivo nominal común en validación, pero la FPR observada en test difiere entre controles. Las comparaciones por familia son descriptivas y exploratorias; no identifican valor incremental de CNN o XGBoost.</t>
         </is>
       </c>
     </row>
@@ -663,7 +673,7 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>En Brent, |z|&gt;3 ocurre el 1.11% de las sesiones frente al 0.27% que predice una normal: 4,1 veces más. Un umbral 3σ no puede separar una cola real de mercado de un defecto de dato.</t>
+          <t>En Brent, |z|&gt;3 ocurre el 1.11% de las sesiones frente al 0.27% de referencia gaussiana. Es una estadística descriptiva estandarizada ex post, no un test de defectos ni evidencia de que 3σ distinga errores de mercado.</t>
         </is>
       </c>
     </row>
@@ -675,7 +685,7 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>No se da ninguna cifra de capital. No se demuestra transferencia a otras asset classes. No se afirma prevalencia real de defectos. Ver hoja 8.</t>
+          <t>No se da ninguna cifra de capital. No se demuestra transferencia a otras asset classes. No se afirma prevalencia real de defectos. Ver hoja 9.</t>
         </is>
       </c>
     </row>
@@ -752,12 +762,12 @@
     <row r="6" ht="42" customHeight="1">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>FPR (tasa de falsas alarmas)</t>
+          <t>FPR realizada</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>De los tramos LIMPIOS, qué fracción levantó alerta igualmente. Es el coste operativo: cada falsa alarma es trabajo de revisión que no encuentra nada. Objetivo fijado: 5 %.</t>
+          <t>De los tramos LIMPIOS, qué fracción levantó alerta igualmente. Es el coste operativo: cada falsa alarma es trabajo de revisión que no encuentra nada. NO se promete un objetivo nominal, porque no se cumple fuera de muestra: se DECLARA la medida. Ver la hoja de punto de operación.</t>
         </is>
       </c>
       <c r="C6" s="7" t="inlineStr">
@@ -769,17 +779,17 @@
     <row r="7" ht="42" customHeight="1">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Recall a presupuesto común</t>
+          <t>Recall a objetivo nominal</t>
         </is>
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>Comparar recalls solo tiene sentido si todos los controles operan a la MISMA carga de alarmas. Si no, el que más alerta parece el más sensible. Todo el Excel está medido así.</t>
+          <t>Los umbrales se fijan en una porción de validación limpia con un objetivo nominal del 5 %. La tasa realizada se mide en el test posterior y puede diferir por deriva y dependencia.</t>
         </is>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
-          <t>recall | FPR = 5 %</t>
+          <t>recall; FPR OOS aparte</t>
         </is>
       </c>
     </row>
@@ -808,7 +818,7 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Nivel de recall que alcanzaría un detector que alertase al azar al 5 %. En las tablas, las celdas en gris están en el azar: ese control NO ve esa familia.</t>
+          <t>Referencia aproximada para un detector aleatorio con prevalencia de alertas del 5 %. En tablas, las celdas en gris están en el azar: ese control NO ve esa familia.</t>
         </is>
       </c>
       <c r="C9" s="7" t="inlineStr">
@@ -897,7 +907,7 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>Estrictamente cronológica, sin mezclar. Entrenamiento hasta 2018-12-31 (558 ventanas). Validación 2019-2023 (236). Test desde 2024-01-05 (124). La CNN se entrena en entrenamiento, el combinador XGBoost en validación y TODO se evalúa en test.</t>
+          <t>Estrictamente cronológica, sin mezclar. Entrenamiento hasta 2018-12-31 (558 ventanas). Validación 2019-2023 (236), separada en ajuste temprano y calibración posterior con purga por solapamiento. CNN y XGBoost se ajustan sin test; los umbrales se congelan antes de evaluar el bloque desde 2024-01-05 (124 ventanas).</t>
         </is>
       </c>
     </row>
@@ -921,7 +931,7 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>Gate conforme-adaptativo (Adaptive Conformal Inference). El umbral se calibra sobre tramos limpios de VALIDACIÓN y se reajusta en línea con la falsa alarma observada, sin suponer una forma de distribución — que es donde falla un 3σ paramétrico sobre estas colas. La garantía NO es incondicional: depende de la dependencia entre ventanas, del drift y del tamaño de la muestra de calibración, y aquí las ventanas solapan.</t>
+          <t>Umbral empírico de orden estadístico calibrado en un segmento tardío de validación, separado del ajuste por una purga de ventanas solapadas. Queda congelado antes del test. La FPR de test se informa sin feedback; no se reclama garantía conformal ni control bajo drift.</t>
         </is>
       </c>
     </row>
@@ -975,13 +985,207 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q13"/>
+  <dimension ref="A1:H13"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="18" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>3 Punto de operación</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>LA HOJA QUE HAY QUE LEER PARA DIMENSIONAR LA REVISIÓN. El gate no promete una tasa nominal de falsas alarmas, porque no se cumple fuera de muestra: declara la medida. Elige la fila por capacidad de revisión disponible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>α nominal pedido</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>FPR REALIZADA</t>
+        </is>
+      </c>
+      <c r="C4" s="3" t="inlineStr">
+        <is>
+          <t>dispersión</t>
+        </is>
+      </c>
+      <c r="D4" s="3" t="inlineStr">
+        <is>
+          <t>exceso sobre nominal</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
+          <t>recall medio</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="n">
+        <v>0.005</v>
+      </c>
+      <c r="B5" s="10" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>± 0.004</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>16.7x</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>0.605</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="9" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="B6" s="10" t="n">
+        <v>0.083</v>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>± 0.004</t>
+        </is>
+      </c>
+      <c r="D6" s="9" t="inlineStr">
+        <is>
+          <t>8.3x</t>
+        </is>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>0.608</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="9" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="B7" s="10" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>± 0.004</t>
+        </is>
+      </c>
+      <c r="D7" s="9" t="inlineStr">
+        <is>
+          <t>5.0x</t>
+        </is>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>0.616</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="9" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="B8" s="10" t="n">
+        <v>0.116</v>
+      </c>
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>± 0.004</t>
+        </is>
+      </c>
+      <c r="D8" s="9" t="inlineStr">
+        <is>
+          <t>2.3x</t>
+        </is>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>0.646</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="9" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="B9" s="10" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>± 0.011</t>
+        </is>
+      </c>
+      <c r="D9" s="9" t="inlineStr">
+        <is>
+          <t>2.0x</t>
+        </is>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="11" ht="46" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>SUELO MEDIDO: el gate no baja de 0.083 de ventanas limpias marcadas. Pedir un α de 0,005 o de 0,010 da exactamente lo mismo, así que dimensionar la revisión suponiendo un 5 % o un 1 % es dimensionar mal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="46" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
+        <is>
+          <t>Por encima del suelo el intercambio es real y suave: más carga de revisión compra más cobertura. El punto se elige por capacidad disponible, no por un número de referencia.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="46" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>El exceso sobre el nominal tiene dos causas medidas. La resolución de la muestra de calibración ya está corregida ampliando la ventana. La que queda es deriva: cada control realiza ~2,6 veces su tasa nominal porque el tramo reciente no predice la cola del siguiente. Esa es la que fija el suelo y no se arregla repartiendo mejor.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="4">
+    <mergeCell ref="A11:E11"/>
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A13:E13"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
     <col width="8" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="13" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="13" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
@@ -995,19 +1199,20 @@
     <col width="13" customWidth="1" min="15" max="15"/>
     <col width="13" customWidth="1" min="16" max="16"/>
     <col width="13" customWidth="1" min="17" max="17"/>
+    <col width="13" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>3 Cobertura</t>
+          <t>4 Cobertura</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Recall por control y familia, a presupuesto de falsas alarmas común (5%). Azar ≈ 0.048; en gris lo que está en el azar. «Reescribe historia» = el defecto altera datos ya publicados; «dato nuevo» = solo afecta a las sesiones recientes.</t>
+          <t>Recall por control y familia; objetivo nominal de calibración 5%, FPR de test observada y no igualada. Azar ≈ 0.048; en gris lo que está en el azar. «Reescribe historia» = el defecto altera datos ya publicados; «dato nuevo» = solo afecta a las sesiones recientes.</t>
         </is>
       </c>
     </row>
@@ -1029,83 +1234,88 @@
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
+          <t>FPR test</t>
+        </is>
+      </c>
+      <c r="E4" s="3" t="inlineStr">
+        <is>
           <t>stale
 (reescribe)</t>
         </is>
       </c>
-      <c r="E4" s="3" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>reversible_jump
 (reescribe)</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>decoupling
 (reescribe)</t>
         </is>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="H4" s="3" t="inlineStr">
         <is>
           <t>lag1_calendar
 (reescribe)</t>
         </is>
       </c>
-      <c r="H4" s="3" t="inlineStr">
+      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>weekly_ffill
 (reescribe)</t>
         </is>
       </c>
-      <c r="I4" s="3" t="inlineStr">
+      <c r="J4" s="3" t="inlineStr">
         <is>
           <t>source_switch
 (reescribe)</t>
         </is>
       </c>
-      <c r="J4" s="3" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
         <is>
           <t>quantize
 (reescribe)</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
+      <c r="L4" s="3" t="inlineStr">
         <is>
           <t>stale
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="L4" s="3" t="inlineStr">
+      <c r="M4" s="3" t="inlineStr">
         <is>
           <t>reversible_jump
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="M4" s="3" t="inlineStr">
+      <c r="N4" s="3" t="inlineStr">
         <is>
           <t>decoupling
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="N4" s="3" t="inlineStr">
+      <c r="O4" s="3" t="inlineStr">
         <is>
           <t>lag1_calendar
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="O4" s="3" t="inlineStr">
+      <c r="P4" s="3" t="inlineStr">
         <is>
           <t>weekly_ffill
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="Q4" s="3" t="inlineStr">
         <is>
           <t>source_switch
 (dato nuevo)</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="R4" s="3" t="inlineStr">
         <is>
           <t>quantize
 (dato nuevo)</t>
@@ -1113,501 +1323,525 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>retorno_3sigma</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="12" t="inlineStr">
         <is>
           <t>Gate A</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>retorno</t>
         </is>
       </c>
-      <c r="D5" s="10" t="n">
+      <c r="D5" s="12" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="E5" s="13" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="F5" s="14" t="n">
+        <v>0.879</v>
+      </c>
+      <c r="G5" s="15" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="H5" s="15" t="n">
+        <v>0.347</v>
+      </c>
+      <c r="I5" s="15" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="J5" s="15" t="n">
+        <v>0.438</v>
+      </c>
+      <c r="K5" s="13" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="L5" s="13" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="M5" s="14" t="n">
+        <v>0.866</v>
+      </c>
+      <c r="N5" s="13" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="O5" s="13" t="n">
+        <v>0.234</v>
+      </c>
+      <c r="P5" s="13" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="Q5" s="15" t="n">
+        <v>0.433</v>
+      </c>
+      <c r="R5" s="13" t="n">
+        <v>0.199</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>retorno_cross_asset</t>
+        </is>
+      </c>
+      <c r="B6" s="12" t="inlineStr">
+        <is>
+          <t>Gate B</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>retorno</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="n">
+        <v>0.387</v>
+      </c>
+      <c r="E6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" s="14" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="G6" s="14" t="n">
+        <v>0.997</v>
+      </c>
+      <c r="H6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J6" s="14" t="n">
+        <v>0.782</v>
+      </c>
+      <c r="K6" s="15" t="n">
+        <v>0.403</v>
+      </c>
+      <c r="L6" s="16" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="M6" s="14" t="n">
+        <v>0.957</v>
+      </c>
+      <c r="N6" s="14" t="n">
+        <v>0.844</v>
+      </c>
+      <c r="O6" s="14" t="n">
+        <v>0.839</v>
+      </c>
+      <c r="P6" s="16" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="Q6" s="14" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="R6" s="15" t="n">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>retorno_cnn</t>
+        </is>
+      </c>
+      <c r="B7" s="12" t="inlineStr">
+        <is>
+          <t>Gate B</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>retorno</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="E7" s="14" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="F7" s="14" t="n">
+        <v>0.925</v>
+      </c>
+      <c r="G7" s="14" t="n">
+        <v>0.984</v>
+      </c>
+      <c r="H7" s="14" t="n">
+        <v>0.753</v>
+      </c>
+      <c r="I7" s="14" t="n">
+        <v>0.8090000000000001</v>
+      </c>
+      <c r="J7" s="16" t="n">
+        <v>0.594</v>
+      </c>
+      <c r="K7" s="15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L7" s="15" t="n">
+        <v>0.395</v>
+      </c>
+      <c r="M7" s="14" t="n">
+        <v>0.901</v>
+      </c>
+      <c r="N7" s="16" t="n">
+        <v>0.629</v>
+      </c>
+      <c r="O7" s="16" t="n">
+        <v>0.503</v>
+      </c>
+      <c r="P7" s="15" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="Q7" s="16" t="n">
+        <v>0.586</v>
+      </c>
+      <c r="R7" s="15" t="n">
+        <v>0.285</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>precio_reticula</t>
+        </is>
+      </c>
+      <c r="B8" s="12" t="inlineStr">
+        <is>
+          <t>Gate B</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>precio</t>
+        </is>
+      </c>
+      <c r="D8" s="12" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="16" t="n">
+        <v>0.613</v>
+      </c>
+      <c r="F8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="17" t="n">
+        <v>0.027</v>
+      </c>
+      <c r="J8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>canal_coherencia</t>
+        </is>
+      </c>
+      <c r="B9" s="12" t="inlineStr">
+        <is>
+          <t>Gate B</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
+        <is>
+          <t>canal</t>
+        </is>
+      </c>
+      <c r="D9" s="12" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="E9" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F9" s="14" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="H9" s="14" t="n">
+        <v>0.992</v>
+      </c>
+      <c r="I9" s="14" t="n">
+        <v>0.962</v>
+      </c>
+      <c r="J9" s="16" t="n">
+        <v>0.637</v>
+      </c>
+      <c r="K9" s="15" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="L9" s="15" t="n">
+        <v>0.476</v>
+      </c>
+      <c r="M9" s="14" t="n">
+        <v>0.903</v>
+      </c>
+      <c r="N9" s="16" t="n">
+        <v>0.6830000000000001</v>
+      </c>
+      <c r="O9" s="16" t="n">
+        <v>0.669</v>
+      </c>
+      <c r="P9" s="15" t="n">
+        <v>0.358</v>
+      </c>
+      <c r="Q9" s="16" t="n">
+        <v>0.656</v>
+      </c>
+      <c r="R9" s="15" t="n">
+        <v>0.282</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>canal_oscilacion</t>
+        </is>
+      </c>
+      <c r="B10" s="12" t="inlineStr">
+        <is>
+          <t>Gate B</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
+        <is>
+          <t>canal</t>
+        </is>
+      </c>
+      <c r="D10" s="12" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="E10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" s="13" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="G10" s="13" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="H10" s="13" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="I10" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J10" s="13" t="n">
+        <v>0.105</v>
+      </c>
+      <c r="K10" s="13" t="n">
+        <v>0.212</v>
+      </c>
+      <c r="L10" s="15" t="n">
+        <v>0.258</v>
+      </c>
+      <c r="M10" s="13" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="N10" s="13" t="n">
+        <v>0.054</v>
+      </c>
+      <c r="O10" s="13" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="P10" s="13" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="Q10" s="13" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="R10" s="13" t="n">
+        <v>0.118</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>canal_ruptura</t>
+        </is>
+      </c>
+      <c r="B11" s="12" t="inlineStr">
+        <is>
+          <t>Gate B</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>canal</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="E11" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="16" t="n">
+        <v>0.742</v>
+      </c>
+      <c r="G11" s="13" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="H11" s="15" t="n">
+        <v>0.282</v>
+      </c>
+      <c r="I11" s="13" t="n">
+        <v>0.102</v>
+      </c>
+      <c r="J11" s="13" t="n">
+        <v>0.11</v>
+      </c>
+      <c r="K11" s="13" t="n">
+        <v>0.062</v>
+      </c>
+      <c r="L11" s="13" t="n">
+        <v>0.073</v>
+      </c>
+      <c r="M11" s="16" t="n">
+        <v>0.715</v>
+      </c>
+      <c r="N11" s="13" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="O11" s="13" t="n">
+        <v>0.065</v>
+      </c>
+      <c r="P11" s="13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="Q11" s="13" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="R11" s="13" t="n">
         <v>0.056</v>
       </c>
-      <c r="E5" s="11" t="n">
-        <v>0.401</v>
-      </c>
-      <c r="F5" s="10" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="G5" s="10" t="n">
+    </row>
+    <row r="12">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>canal_geometria</t>
+        </is>
+      </c>
+      <c r="B12" s="12" t="inlineStr">
+        <is>
+          <t>Gate B</t>
+        </is>
+      </c>
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>canal</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="n">
         <v>0.089</v>
       </c>
-      <c r="H5" s="10" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="I5" s="10" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="J5" s="10" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="K5" s="10" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="L5" s="11" t="n">
-        <v>0.398</v>
-      </c>
-      <c r="M5" s="10" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="N5" s="10" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="O5" s="10" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="P5" s="10" t="n">
-        <v>0.118</v>
-      </c>
-      <c r="Q5" s="10" t="n">
-        <v>0.056</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>retorno_cross_asset</t>
-        </is>
-      </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="E12" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="15" t="n">
+        <v>0.454</v>
+      </c>
+      <c r="G12" s="13" t="n">
+        <v>0.196</v>
+      </c>
+      <c r="H12" s="13" t="n">
+        <v>0.153</v>
+      </c>
+      <c r="I12" s="15" t="n">
+        <v>0.366</v>
+      </c>
+      <c r="J12" s="13" t="n">
+        <v>0.167</v>
+      </c>
+      <c r="K12" s="13" t="n">
+        <v>0.094</v>
+      </c>
+      <c r="L12" s="13" t="n">
+        <v>0.097</v>
+      </c>
+      <c r="M12" s="15" t="n">
+        <v>0.409</v>
+      </c>
+      <c r="N12" s="13" t="n">
+        <v>0.091</v>
+      </c>
+      <c r="O12" s="13" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="P12" s="13" t="n">
+        <v>0.078</v>
+      </c>
+      <c r="Q12" s="13" t="n">
+        <v>0.226</v>
+      </c>
+      <c r="R12" s="13" t="n">
+        <v>0.089</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>vintage_discrepancia</t>
+        </is>
+      </c>
+      <c r="B13" s="12" t="inlineStr">
         <is>
           <t>Gate B</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>retorno</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="n">
-        <v>0.629</v>
-      </c>
-      <c r="E6" s="11" t="n">
-        <v>0.481</v>
-      </c>
-      <c r="F6" s="12" t="n">
-        <v>0.6830000000000001</v>
-      </c>
-      <c r="G6" s="12" t="n">
-        <v>0.6850000000000001</v>
-      </c>
-      <c r="H6" s="12" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="I6" s="10" t="n">
-        <v>0.151</v>
-      </c>
-      <c r="J6" s="13" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="K6" s="10" t="n">
-        <v>0.081</v>
-      </c>
-      <c r="L6" s="11" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="M6" s="11" t="n">
-        <v>0.253</v>
-      </c>
-      <c r="N6" s="11" t="n">
-        <v>0.282</v>
-      </c>
-      <c r="O6" s="10" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="P6" s="10" t="n">
-        <v>0.167</v>
-      </c>
-      <c r="Q6" s="13" t="n">
-        <v>0.04</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>retorno_cnn</t>
-        </is>
-      </c>
-      <c r="B7" s="9" t="inlineStr">
-        <is>
-          <t>Gate B</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>retorno</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="n">
-        <v>0.696</v>
-      </c>
-      <c r="E7" s="14" t="n">
-        <v>0.793</v>
-      </c>
-      <c r="F7" s="14" t="n">
-        <v>0.839</v>
-      </c>
-      <c r="G7" s="11" t="n">
-        <v>0.492</v>
-      </c>
-      <c r="H7" s="12" t="n">
-        <v>0.57</v>
-      </c>
-      <c r="I7" s="11" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="J7" s="10" t="n">
-        <v>0.062</v>
-      </c>
-      <c r="K7" s="10" t="n">
-        <v>0.137</v>
-      </c>
-      <c r="L7" s="14" t="n">
-        <v>0.755</v>
-      </c>
-      <c r="M7" s="11" t="n">
-        <v>0.366</v>
-      </c>
-      <c r="N7" s="11" t="n">
-        <v>0.269</v>
-      </c>
-      <c r="O7" s="10" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="P7" s="11" t="n">
-        <v>0.309</v>
-      </c>
-      <c r="Q7" s="10" t="n">
-        <v>0.059</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>precio_reticula</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
-        <is>
-          <t>Gate B</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>precio</t>
-        </is>
-      </c>
-      <c r="D8" s="12" t="n">
-        <v>0.613</v>
-      </c>
-      <c r="E8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="G8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="13" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="I8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="J8" s="14" t="n">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>vintage</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="E13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="P8" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q8" s="13" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>canal_coherencia</t>
-        </is>
-      </c>
-      <c r="B9" s="9" t="inlineStr">
-        <is>
-          <t>Gate B</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>canal</t>
-        </is>
-      </c>
-      <c r="D9" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="12" t="n">
-        <v>0.5620000000000001</v>
-      </c>
-      <c r="F9" s="12" t="n">
-        <v>0.656</v>
-      </c>
-      <c r="G9" s="12" t="n">
-        <v>0.677</v>
-      </c>
-      <c r="H9" s="12" t="n">
-        <v>0.578</v>
-      </c>
-      <c r="I9" s="10" t="n">
-        <v>0.218</v>
-      </c>
-      <c r="J9" s="10" t="n">
-        <v>0.059</v>
-      </c>
-      <c r="K9" s="10" t="n">
-        <v>0.129</v>
-      </c>
-      <c r="L9" s="12" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="M9" s="11" t="n">
-        <v>0.293</v>
-      </c>
-      <c r="N9" s="11" t="n">
-        <v>0.25</v>
-      </c>
-      <c r="O9" s="10" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="P9" s="10" t="n">
-        <v>0.239</v>
-      </c>
-      <c r="Q9" s="13" t="n">
-        <v>0.048</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>canal_oscilacion</t>
-        </is>
-      </c>
-      <c r="B10" s="9" t="inlineStr">
-        <is>
-          <t>Gate B</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>canal</t>
-        </is>
-      </c>
-      <c r="D10" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="13" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="F10" s="10" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="H10" s="14" t="n">
-        <v>0.876</v>
-      </c>
-      <c r="I10" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="J10" s="10" t="n">
-        <v>0.097</v>
-      </c>
-      <c r="K10" s="10" t="n">
-        <v>0.145</v>
-      </c>
-      <c r="L10" s="13" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="M10" s="13" t="n">
-        <v>0.022</v>
-      </c>
-      <c r="N10" s="13" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="O10" s="10" t="n">
-        <v>0.102</v>
-      </c>
-      <c r="P10" s="10" t="n">
-        <v>0.051</v>
-      </c>
-      <c r="Q10" s="10" t="n">
-        <v>0.065</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>canal_ruptura</t>
-        </is>
-      </c>
-      <c r="B11" s="9" t="inlineStr">
-        <is>
-          <t>Gate B</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>canal</t>
-        </is>
-      </c>
-      <c r="D11" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="12" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="F11" s="13" t="n">
-        <v>0.035</v>
-      </c>
-      <c r="G11" s="11" t="n">
-        <v>0.274</v>
-      </c>
-      <c r="H11" s="10" t="n">
-        <v>0.091</v>
-      </c>
-      <c r="I11" s="10" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="J11" s="13" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="K11" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L11" s="12" t="n">
-        <v>0.6879999999999999</v>
-      </c>
-      <c r="M11" s="10" t="n">
-        <v>0.078</v>
-      </c>
-      <c r="N11" s="10" t="n">
-        <v>0.065</v>
-      </c>
-      <c r="O11" s="13" t="n">
-        <v>0.027</v>
-      </c>
-      <c r="P11" s="13" t="n">
-        <v>0.043</v>
-      </c>
-      <c r="Q11" s="13" t="n">
-        <v>0.043</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>canal_geometria</t>
-        </is>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Gate B</t>
-        </is>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>canal</t>
-        </is>
-      </c>
-      <c r="D12" s="13" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="11" t="n">
-        <v>0.312</v>
-      </c>
-      <c r="F12" s="10" t="n">
-        <v>0.148</v>
-      </c>
-      <c r="G12" s="10" t="n">
-        <v>0.105</v>
-      </c>
-      <c r="H12" s="11" t="n">
-        <v>0.296</v>
-      </c>
-      <c r="I12" s="10" t="n">
-        <v>0.14</v>
-      </c>
-      <c r="J12" s="10" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="K12" s="13" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="L12" s="11" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="M12" s="10" t="n">
-        <v>0.054</v>
-      </c>
-      <c r="N12" s="10" t="n">
-        <v>0.056</v>
-      </c>
-      <c r="O12" s="13" t="n">
-        <v>0.038</v>
-      </c>
-      <c r="P12" s="10" t="n">
-        <v>0.159</v>
-      </c>
-      <c r="Q12" s="10" t="n">
-        <v>0.062</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>vintage_discrepancia</t>
-        </is>
-      </c>
-      <c r="B13" s="9" t="inlineStr">
-        <is>
-          <t>Gate B</t>
-        </is>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>vintage</t>
-        </is>
-      </c>
-      <c r="D13" s="14" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="12" t="n">
-        <v>0.747</v>
-      </c>
       <c r="F13" s="14" t="n">
-        <v>1</v>
+        <v>0.874</v>
       </c>
       <c r="G13" s="14" t="n">
         <v>1</v>
@@ -1621,26 +1855,29 @@
       <c r="J13" s="14" t="n">
         <v>1</v>
       </c>
-      <c r="K13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="L13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="M13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="N13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="O13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="P13" s="13" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="Q13" s="13" t="n">
-        <v>0.048</v>
+      <c r="K13" s="14" t="n">
+        <v>1</v>
+      </c>
+      <c r="L13" s="15" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="M13" s="15" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="N13" s="15" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="O13" s="15" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="P13" s="15" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="Q13" s="15" t="n">
+        <v>0.468</v>
+      </c>
+      <c r="R13" s="15" t="n">
+        <v>0.468</v>
       </c>
     </row>
   </sheetData>
@@ -1651,7 +1888,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1670,14 +1907,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>4 Gate A vs Gate B</t>
+          <t>5 Gate A vs Gate B</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ATENCIÓN AL LEER ESTA HOJA: cada configuración opera a una tasa de falsas alarmas DISTINTA, así que la diferencia de recall entre filas NO aísla el valor incremental de ninguna capa. Se incluye porque describe el punto de operación de cada configuración, no como medida de mejora. La comparación que sí es válida —control contra control a presupuesto común— está en la hoja 3.</t>
+          <t>Los umbrales se calibran con el mismo objetivo nominal en validación, pero la FPR realizada en test difiere. Las diferencias de recall son descriptivas y no aíslan el valor incremental de ninguna capa. Este benchmark mide controles en paralelo; no valida un router secuencial.</t>
         </is>
       </c>
     </row>
@@ -1694,7 +1931,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t>Falsas alarmas medidas</t>
+          <t>FPR observada en test</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
@@ -1720,13 +1957,13 @@
         </is>
       </c>
       <c r="C5" s="5" t="n">
-        <v>0.032</v>
+        <v>0.194</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>0.074</v>
+        <v>0.371</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.032</v>
+        <v>0.194</v>
       </c>
     </row>
     <row r="6">
@@ -1741,13 +1978,13 @@
         </is>
       </c>
       <c r="C6" s="5" t="n">
-        <v>0.081</v>
+        <v>0.758</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>0.579</v>
+        <v>0.946</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.078</v>
+        <v>0.774</v>
       </c>
     </row>
     <row r="7">
@@ -1762,29 +1999,29 @@
         </is>
       </c>
       <c r="C7" s="5" t="n">
-        <v>0.083</v>
+        <v>0.774</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>0.606</v>
+        <v>0.951</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.083</v>
+        <v>0.788</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="15" t="inlineStr">
-        <is>
-          <t>Aportación marginal de la CNN sobre el banco</t>
-        </is>
-      </c>
-      <c r="D9" s="15" t="n">
-        <v>0.026</v>
+      <c r="A9" s="18" t="inlineStr">
+        <is>
+          <t>Diferencia descriptiva: banco con CNN menos banco sin CNN</t>
+        </is>
+      </c>
+      <c r="D9" s="18" t="n">
+        <v>0.006</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>Esa diferencia marginal es la única de esta hoja medida entre dos configuraciones a falsas alarmas casi iguales (0,081 y 0,083), así que es la única interpretable como aportación. Las demás filas difieren también en punto de operación.</t>
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>Diferencia exploratoria post hoc sobre el mismo test; no es una estimación confirmatoria de aportación incremental. Requiere test externo y protocolo preespecificado.</t>
         </is>
       </c>
     </row>
@@ -1796,7 +2033,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1816,14 +2053,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>5 Familias</t>
+          <t>6 Familias</t>
         </is>
       </c>
     </row>
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Qué es cada familia de defecto y qué control la cubre mejor.</t>
+          <t>Mejor control observado por familia, selección post hoc en el mismo test; lectura exploratoria.</t>
         </is>
       </c>
     </row>
@@ -1860,7 +2097,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="9" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
         <is>
           <t>stale</t>
         </is>
@@ -1870,189 +2107,189 @@
           <t>Cotización repetida: el precio deja de moverse (check TRIM de ≥20 ceros).</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>canal_coherencia</t>
         </is>
       </c>
-      <c r="D5" s="17" t="n">
+      <c r="D5" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E5" s="9" t="inlineStr">
+      <c r="E5" s="12" t="inlineStr">
+        <is>
+          <t>retorno_cross_asset</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="n">
+        <v>0.637</v>
+      </c>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>reversible_jump</t>
+        </is>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>Tick erróneo que revierte al día siguiente.</t>
+        </is>
+      </c>
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>retorno_cross_asset</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="n">
+        <v>0.968</v>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>retorno_cross_asset</t>
+        </is>
+      </c>
+      <c r="F6" s="20" t="n">
+        <v>0.957</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>decoupling</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>Desalineación de fechas de varias sesiones frente a los pares.</t>
+        </is>
+      </c>
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>vintage_discrepancia</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>retorno_cross_asset</t>
+        </is>
+      </c>
+      <c r="F7" s="20" t="n">
+        <v>0.844</v>
+      </c>
+    </row>
+    <row r="8" ht="30" customHeight="1">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>lag1_calendar</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>Desfase de UNA sesión. Es la forma del defecto real de EURUSD de 2008.</t>
+        </is>
+      </c>
+      <c r="C8" s="12" t="inlineStr">
+        <is>
+          <t>retorno_cross_asset</t>
+        </is>
+      </c>
+      <c r="D8" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E8" s="12" t="inlineStr">
+        <is>
+          <t>retorno_cross_asset</t>
+        </is>
+      </c>
+      <c r="F8" s="20" t="n">
+        <v>0.839</v>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>weekly_ffill</t>
+        </is>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>Fuente semanal propagada a diario: el precio solo cambia 1 de cada 5 días.</t>
+        </is>
+      </c>
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>canal_oscilacion</t>
         </is>
       </c>
-      <c r="F5" s="18" t="n">
-        <v>0.145</v>
-      </c>
-    </row>
-    <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>reversible_jump</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>Tick erróneo que revierte al día siguiente.</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>retorno_cnn</t>
-        </is>
-      </c>
-      <c r="D6" s="17" t="n">
-        <v>0.793</v>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>retorno_cnn</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="n">
-        <v>0.755</v>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>decoupling</t>
-        </is>
-      </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>Desalineación de fechas de varias sesiones frente a los pares.</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="D9" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E9" s="12" t="inlineStr">
+        <is>
+          <t>retorno_cross_asset</t>
+        </is>
+      </c>
+      <c r="F9" s="21" t="n">
+        <v>0.53</v>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>source_switch</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Empalme de proveedores: salto de nivel a mitad de tramo sin corregir.</t>
+        </is>
+      </c>
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D7" s="17" t="n">
+      <c r="D10" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>retorno_cnn</t>
-        </is>
-      </c>
-      <c r="F7" s="19" t="n">
-        <v>0.366</v>
-      </c>
-    </row>
-    <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>lag1_calendar</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>Desfase de UNA sesión. Es la forma del defecto real de EURUSD de 2008.</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="E10" s="12" t="inlineStr">
+        <is>
+          <t>retorno_cross_asset</t>
+        </is>
+      </c>
+      <c r="F10" s="20" t="n">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="11" ht="30" customHeight="1">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>quantize</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Pérdida de precisión del feed: la cotización se trunca a menos decimales.</t>
+        </is>
+      </c>
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>precio_reticula</t>
+        </is>
+      </c>
+      <c r="D11" s="20" t="n">
+        <v>1</v>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
         <is>
           <t>vintage_discrepancia</t>
         </is>
       </c>
-      <c r="D8" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>retorno_cross_asset</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="n">
-        <v>0.282</v>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>weekly_ffill</t>
-        </is>
-      </c>
-      <c r="B9" s="5" t="inlineStr">
-        <is>
-          <t>Fuente semanal propagada a diario: el precio solo cambia 1 de cada 5 días.</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>vintage_discrepancia</t>
-        </is>
-      </c>
-      <c r="D9" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>retorno_cnn</t>
-        </is>
-      </c>
-      <c r="F9" s="18" t="n">
-        <v>0.105</v>
-      </c>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>source_switch</t>
-        </is>
-      </c>
-      <c r="B10" s="5" t="inlineStr">
-        <is>
-          <t>Empalme de proveedores: salto de nivel a mitad de tramo sin corregir.</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>vintage_discrepancia</t>
-        </is>
-      </c>
-      <c r="D10" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>retorno_cnn</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="n">
-        <v>0.309</v>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>quantize</t>
-        </is>
-      </c>
-      <c r="B11" s="5" t="inlineStr">
-        <is>
-          <t>Pérdida de precisión del feed: la cotización se trunca a menos decimales.</t>
-        </is>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>precio_reticula</t>
-        </is>
-      </c>
-      <c r="D11" s="17" t="n">
-        <v>1</v>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>canal_oscilacion</t>
-        </is>
-      </c>
-      <c r="F11" s="18" t="n">
-        <v>0.065</v>
+      <c r="F11" s="22" t="n">
+        <v>0.468</v>
       </c>
     </row>
   </sheetData>
@@ -2063,7 +2300,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2081,7 +2318,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>6 Modelos aguas abajo</t>
+          <t>7 Modelos aguas abajo</t>
         </is>
       </c>
     </row>
@@ -2120,7 +2357,7 @@
           <t>VaR FHS-EWMA condicional a volatilidad</t>
         </is>
       </c>
-      <c r="B5" s="20" t="inlineStr">
+      <c r="B5" s="23" t="inlineStr">
         <is>
           <t>Supera el backtest</t>
         </is>
@@ -2142,7 +2379,7 @@
           <t>Supervivencia del canal · XGB-AFT</t>
         </is>
       </c>
-      <c r="B6" s="20" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t>Supera el backtest</t>
         </is>
@@ -2164,7 +2401,7 @@
           <t>Detección de canal · CNN EfficientNet</t>
         </is>
       </c>
-      <c r="B7" s="21" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>Pasa como clasificador, no como estrategia</t>
         </is>
@@ -2188,7 +2425,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2205,7 +2442,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>7 Estado</t>
+          <t>8 Estado</t>
         </is>
       </c>
     </row>
@@ -2246,14 +2483,14 @@
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>Cada familia de defecto la cubre bien un control distinto y varias las ve uno solo. Medido con defectos de verdad conocida sobre test temporal y presupuesto de falsas alarmas común. Pendiente de auditoría cruzada.</t>
+          <t>Los controles muestran perfiles de cobertura distintos y varias familias quedan cubiertas por un único control en este test. Medido con defectos de verdad conocida sobre test temporal y presupuesto de falsas alarmas nominal calibrado en validación; la FPR se mide en test y puede diferir. Pendiente de auditoría cruzada.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="52" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Calibración conforme del umbral</t>
+          <t>Calibración empírica del umbral</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
@@ -2263,7 +2500,7 @@
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>El gate conforme-adaptativo alcanza el presupuesto de falsas alarmas fijado sin suponer una forma de distribución. Un umbral paramétrico 3σ no lo consigue sobre estas colas.</t>
+          <t>Se congela un umbral empírico usando un bloque de validación separado y purgado. No se reclama garantía conformal ni control de FPR bajo drift.</t>
         </is>
       </c>
     </row>
@@ -2292,12 +2529,12 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>🟡 provisional</t>
+          <t>🟡 exploratorio</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>Es el mejor control en las familias sin estadístico cerrado evidente, y el que más cubre en el escenario de dato nuevo. La mejora sobre el banco completo es real y modesta.</t>
+          <t>La evaluación sintética no demuestra superioridad generalizable. La selección de ganadores se hace sobre el mismo test; hacen falta prueba externa y etiquetas reales.</t>
         </is>
       </c>
     </row>
@@ -2307,14 +2544,14 @@
           <t>XGBoost como combinador</t>
         </is>
       </c>
-      <c r="B9" s="21" t="inlineStr">
-        <is>
-          <t>🟡 provisional · resultado negativo</t>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>🟡 no concluyente</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>Rinde por debajo de la unión de los mismos controles con umbral propio, y diluye los controles que resuelven una familia de forma exacta. Se publica como negativo.</t>
+          <t>Su recall y el de la unión se observan con FPR OOS distintas. No se puede afirmar que uno supere al otro sin comparar a un mismo punto de operación o sobre curvas ROC/PR.</t>
         </is>
       </c>
     </row>
@@ -2343,13 +2580,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -2359,7 +2596,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>8 Limitaciones</t>
+          <t>9 Limitaciones</t>
         </is>
       </c>
     </row>
@@ -2433,34 +2670,46 @@
     <row r="9" ht="42" customHeight="1">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>FPR no idénticas</t>
+          <t>FPR observada no igualada</t>
         </is>
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>Gate A opera a 0,032 y Gate B a 0,083 de falsas alarmas: la comparación es generosa en alarmas para Gate B.</t>
+          <t>La FPR de test puede diferir entre controles pese a calibrar umbrales al mismo objetivo nominal; no interpretar recall como comparación a operación idéntica.</t>
         </is>
       </c>
     </row>
     <row r="10" ht="42" customHeight="1">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>Un solo activo y un solo panel</t>
+          <t>Resolución de calibración</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>Todo el banco se ha medido sobre Brent y sus cuatro pares. La transferencia a otras asset classes NO está demostrada.</t>
+          <t>El bloque de calibración es finito. La cuota de Bonferroni por control puede quedar por debajo de una observación (1/n), en cuyo caso el umbral empírico se sitúa en el máximo de calibración y no puede realizar exactamente el objetivo nominal.</t>
         </is>
       </c>
     </row>
     <row r="11" ht="42" customHeight="1">
       <c r="A11" s="6" t="inlineStr">
         <is>
+          <t>Un solo activo y un solo panel</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Todo el banco se ha medido sobre Brent y sus cuatro pares. La transferencia a otras asset classes NO está demostrada.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="42" customHeight="1">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
           <t>Capital</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B12" s="5" t="inlineStr">
         <is>
           <t>No se reporta ninguna cifra de capital. Sería k·VaR con el semáforo de Basilea, pero exigiría cartera real, correlaciones, diversificación entre mesas, específico y default, PLA por mesa, NMRF y suelo SA.</t>
         </is>

--- a/results/reports/dq_entregables/resultados_dq.xlsx
+++ b/results/reports/dq_entregables/resultados_dq.xlsx
@@ -985,7 +985,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H13"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -1158,16 +1158,24 @@
     <row r="13" ht="46" customHeight="1">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t>El exceso sobre el nominal tiene dos causas medidas. La resolución de la muestra de calibración ya está corregida ampliando la ventana. La que queda es deriva: cada control realiza ~2,6 veces su tasa nominal porque el tramo reciente no predice la cola del siguiente. Esa es la que fija el suelo y no se arregla repartiendo mejor.</t>
+          <t>POR QUÉ EXISTE EL SUELO: las ventanas de 20 sesiones con paso 5 solapan al 75 %, así que una recalibración de 236 puntuaciones contiene solo 59 observaciones EFECTIVAS. Con 7 controles estadísticos, el α más pequeño que esa muestra puede representar es 7/59 = 0.119. Por debajo, la petición no es representable: el umbral cae en el máximo empírico y el gate entrega su suelo. El suelo es consecuencia del tamaño de la muestra, no una curiosidad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="46" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>CORRECCIÓN REGISTRADA: una versión anterior atribuía el exceso a «resolución corregida más deriva de 2,6x». Esa atribución contaba las puntuaciones consecutivas como independientes y queda RETIRADA. El suelo y la curva no se ven afectados: son observaciones, no atribuciones causales.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="A11:E11"/>
+  <mergeCells count="5">
     <mergeCell ref="A12:E12"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A11:E11"/>
     <mergeCell ref="A13:E13"/>
+    <mergeCell ref="A14:E14"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
